--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\BPMCCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF249023-3B75-4723-847B-C8191E189920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFB81C3-6986-46A3-B05D-B75EF1AC9D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6825" yWindow="4485" windowWidth="17280" windowHeight="10005" tabRatio="846" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="465" yWindow="795" windowWidth="25770" windowHeight="20955" tabRatio="846" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="6" r:id="rId1"/>
@@ -783,10 +783,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>*2021년도 값 제외하기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt; 연도별 풍력·태양광 보급 (단위: MW) &gt;</t>
   </si>
   <si>
@@ -812,6 +808,9 @@
   </si>
   <si>
     <t>2026-09-04: hydro 2025 mandated build (1,815 MW) removed - the source cell was the cumulative conventional hydro fleet total, not an addition. EPS hydro capacity had jumped 2.1 -&gt; 3.9 GW in 2025 (actual fleet ~1.8 GW).</t>
+  </si>
+  <si>
+    <t>2026-09-14 partner round 2 file adopted (260911): hard coal 2021 mandated build 3,098 MW (Goseong Hai 1-2 2,080 MW, Shin-Seocheon 1 1,018 MW) added in the 설비현황 tab. Consistent with the start-year convention: BHRaSYC hard coal is the end-2020 fleet (rebuilt from the EPSIS unit list the same day), so 2021 = end-2020 fleet + this build - the 2,620 MW retired in BCRbQ 2021 = 36.97 GW vs KPX 36.94 GW.</t>
   </si>
 </sst>
 </file>
@@ -993,7 +992,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1087,6 +1086,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7979"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1406,7 +1411,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1613,6 +1618,7 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2035,6 +2041,11 @@
         <v>31</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>220</v>
+      </c>
+    </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>32</v>
@@ -2128,7 +2139,7 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -2136,7 +2147,7 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -3096,12 +3107,12 @@
     </row>
     <row r="103" spans="1:17">
       <c r="A103" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="104" spans="1:17">
       <c r="A104" s="92" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B104" s="93">
         <v>2023</v>
@@ -3326,12 +3337,12 @@
     </row>
     <row r="109" spans="1:17">
       <c r="A109" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="110" spans="1:17">
       <c r="A110" s="92" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B110" s="92" t="s">
         <v>97</v>
@@ -3340,7 +3351,7 @@
         <v>111</v>
       </c>
       <c r="D110" s="92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E110" s="92" t="s">
         <v>112</v>
@@ -3349,7 +3360,7 @@
         <v>95</v>
       </c>
       <c r="G110" s="92" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H110" s="92" t="s">
         <v>101</v>
@@ -3357,7 +3368,7 @@
     </row>
     <row r="111" spans="1:17">
       <c r="A111" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B111" s="95">
         <v>0</v>
@@ -3723,8 +3734,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D25" s="49">
-        <v>0</v>
+      <c r="D25" s="96">
+        <f t="shared" si="0"/>
+        <v>3098</v>
       </c>
       <c r="E25" s="7">
         <f t="shared" si="0"/>
@@ -3742,9 +3754,6 @@
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="I25" t="s">
-        <v>211</v>
-      </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="7" t="s">
@@ -3843,7 +3852,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="7">
-        <f t="shared" ref="B29:H29" si="3">C6</f>
+        <f t="shared" ref="B29:G29" si="3">C6</f>
         <v>0</v>
       </c>
       <c r="C29" s="7">
@@ -3870,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4460,51 +4469,51 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="101" t="s">
+      <c r="A5" s="99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="101"/>
-      <c r="L5" s="101" t="s">
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="M5" s="104" t="s">
+      <c r="M5" s="105" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="99"/>
-      <c r="B6" s="102" t="s">
+      <c r="A6" s="100"/>
+      <c r="B6" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102" t="s">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102" t="s">
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="L6" s="102"/>
-      <c r="M6" s="105"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="106"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A7" s="100"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="24" t="s">
         <v>97</v>
       </c>
@@ -4532,12 +4541,12 @@
       <c r="J7" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="106"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="107"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="107">
+      <c r="A8" s="108">
         <v>2024</v>
       </c>
       <c r="B8" s="22">
@@ -4578,7 +4587,7 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="96"/>
+      <c r="A9" s="97"/>
       <c r="B9" s="17">
         <v>4025</v>
       </c>
@@ -4613,7 +4622,7 @@
       <c r="M9" s="20"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="96">
+      <c r="A10" s="97">
         <v>2025</v>
       </c>
       <c r="B10" s="16">
@@ -4654,7 +4663,7 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="96"/>
+      <c r="A11" s="97"/>
       <c r="B11" s="17">
         <v>4571</v>
       </c>
@@ -4689,7 +4698,7 @@
       <c r="M11" s="20"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="96">
+      <c r="A12" s="97">
         <v>2026</v>
       </c>
       <c r="B12" s="16">
@@ -4730,7 +4739,7 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="96"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="17">
         <v>5161</v>
       </c>
@@ -4765,7 +4774,7 @@
       <c r="M13" s="20"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="96">
+      <c r="A14" s="97">
         <v>2027</v>
       </c>
       <c r="B14" s="16">
@@ -4806,7 +4815,7 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="96"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="17">
         <v>5780</v>
       </c>
@@ -4841,7 +4850,7 @@
       <c r="M15" s="20"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="96">
+      <c r="A16" s="97">
         <v>2028</v>
       </c>
       <c r="B16" s="16">
@@ -4882,7 +4891,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="96"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="17">
         <v>6409</v>
       </c>
@@ -4917,7 +4926,7 @@
       <c r="M17" s="20"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="96">
+      <c r="A18" s="97">
         <v>2029</v>
       </c>
       <c r="B18" s="16">
@@ -4958,7 +4967,7 @@
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="96"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="17">
         <v>7046</v>
       </c>
@@ -4993,7 +5002,7 @@
       <c r="M19" s="20"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="96">
+      <c r="A20" s="97">
         <v>2030</v>
       </c>
       <c r="B20" s="16">
@@ -5034,7 +5043,7 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="96"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="17">
         <v>7962</v>
       </c>
@@ -5069,7 +5078,7 @@
       <c r="M21" s="20"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="96">
+      <c r="A22" s="97">
         <v>2031</v>
       </c>
       <c r="B22" s="16">
@@ -5110,7 +5119,7 @@
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="96"/>
+      <c r="A23" s="97"/>
       <c r="B23" s="17">
         <v>8396</v>
       </c>
@@ -5145,7 +5154,7 @@
       <c r="M23" s="20"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="96">
+      <c r="A24" s="97">
         <v>2032</v>
       </c>
       <c r="B24" s="16">
@@ -5186,7 +5195,7 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="96"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="17">
         <v>8829</v>
       </c>
@@ -5221,7 +5230,7 @@
       <c r="M25" s="20"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="96">
+      <c r="A26" s="97">
         <v>2033</v>
       </c>
       <c r="B26" s="16">
@@ -5262,7 +5271,7 @@
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="96"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="17">
         <v>9261</v>
       </c>
@@ -5297,7 +5306,7 @@
       <c r="M27" s="20"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="96">
+      <c r="A28" s="97">
         <v>2034</v>
       </c>
       <c r="B28" s="16">
@@ -5338,7 +5347,7 @@
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="96"/>
+      <c r="A29" s="97"/>
       <c r="B29" s="17">
         <v>9693</v>
       </c>
@@ -5373,7 +5382,7 @@
       <c r="M29" s="20"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="96">
+      <c r="A30" s="97">
         <v>2035</v>
       </c>
       <c r="B30" s="16">
@@ -5414,7 +5423,7 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="96"/>
+      <c r="A31" s="97"/>
       <c r="B31" s="17">
         <v>10126</v>
       </c>
@@ -5449,7 +5458,7 @@
       <c r="M31" s="20"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="96">
+      <c r="A32" s="97">
         <v>2036</v>
       </c>
       <c r="B32" s="16">
@@ -5490,7 +5499,7 @@
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="96"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="17">
         <v>10431</v>
       </c>
@@ -5525,7 +5534,7 @@
       <c r="M33" s="20"/>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" s="96">
+      <c r="A34" s="97">
         <v>2037</v>
       </c>
       <c r="B34" s="16">
@@ -5566,7 +5575,7 @@
       </c>
     </row>
     <row r="35" spans="1:17">
-      <c r="A35" s="96"/>
+      <c r="A35" s="97"/>
       <c r="B35" s="17">
         <v>10735</v>
       </c>
@@ -5601,7 +5610,7 @@
       <c r="M35" s="20"/>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="96">
+      <c r="A36" s="97">
         <v>2038</v>
       </c>
       <c r="B36" s="16">
@@ -5642,7 +5651,7 @@
       </c>
     </row>
     <row r="37" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A37" s="97"/>
+      <c r="A37" s="98"/>
       <c r="B37" s="18">
         <v>11040</v>
       </c>
@@ -9916,7 +9925,7 @@
       </c>
       <c r="D2" s="76">
         <f>'설비현황_19~25'!D25</f>
-        <v>0</v>
+        <v>3098</v>
       </c>
       <c r="E2" s="76">
         <f>'설비현황_19~25'!E25</f>
@@ -13095,20 +13104,12 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="688c5d3b-a76a-458b-b159-91c2a1154680">
@@ -13118,7 +13119,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010027350D42B0D95040ACC873ED5DCB146E" ma:contentTypeVersion="10" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="c2e4f52adf7af47ba555973ff8cbcabe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="688c5d3b-a76a-458b-b159-91c2a1154680" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="502e33886199ad3dabc1cc93359c84e5" ns2:_="">
     <xsd:import namespace="688c5d3b-a76a-458b-b159-91c2a1154680"/>
@@ -13294,15 +13295,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AC0E8B6-FC6C-47AD-8E91-EBF41CCB1712}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13444BB4-D2AE-4704-9F59-09418FDD2FE0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -13312,7 +13314,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C8EFB68-B099-4082-B802-B144AFACC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13330,6 +13332,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AC0E8B6-FC6C-47AD-8E91-EBF41CCB1712}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" enabled="0" method="" siteId="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" removed="1"/>

--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\BPMCCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFB81C3-6986-46A3-B05D-B75EF1AC9D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A16E22-8226-4575-9619-D2F18A83CCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="465" yWindow="795" windowWidth="25770" windowHeight="20955" tabRatio="846" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15450" tabRatio="846" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="6" r:id="rId1"/>
@@ -51,7 +51,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>2026-09-04: 124.044 MW moved here from BHRaSYC-StartYearCapacities Vintage2021 (source sheet shows 0 for 2021); start-year vintages must end in 2020.</t>
         </r>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="230">
   <si>
     <t>연도</t>
   </si>
@@ -663,10 +663,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1. 태양광 누적 설비 용량</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>2. 해상풍력 누적 설비용량</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -811,6 +807,39 @@
   </si>
   <si>
     <t>2026-09-14 partner round 2 file adopted (260911): hard coal 2021 mandated build 3,098 MW (Goseong Hai 1-2 2,080 MW, Shin-Seocheon 1 1,018 MW) added in the 설비현황 tab. Consistent with the start-year convention: BHRaSYC hard coal is the end-2020 fleet (rebuilt from the EPSIS unit list the same day), so 2021 = end-2020 fleet + this build - the 2,620 MW retired in BCRbQ 2021 = 36.97 GW vs KPX 36.94 GW.</t>
+  </si>
+  <si>
+    <t>에너지원별(1)</t>
+  </si>
+  <si>
+    <t>에너지원별(2)</t>
+  </si>
+  <si>
+    <t>에너지원별(3)</t>
+  </si>
+  <si>
+    <t>에너지원별(4)</t>
+  </si>
+  <si>
+    <t>① 재생에너지</t>
+  </si>
+  <si>
+    <t>http://kosis.kr/statHtml/statHtml.do?orgId=337&amp;tblId=DT_337N_A005A&amp;tmprScrId=20260915155812527_1919405ca6b44674</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 태양광 누적 설비 용량(KOSIS/ 신재생에너지 보급용량(발전-누적)/2026.9.15)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=337&amp;tblId=DT_337N_A005A</t>
+  </si>
+  <si>
+    <t>통계청 KOSIS 신재생에너지 보급용량(발전-누적)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-09-15 partner round 3 file adopted (260915): grid-connected solar 2020-2025 rebuilt as year-on-year differences of the KEA/KOSIS cumulative 'utility/business use' series (one source for the whole period), removing the 2024 discontinuity where two sources had been joined (2024 build 5,568 -&gt; 3,196 MW; 2021 3,956 -&gt; 3,428). Mandated solar 2021-2038 now totals 61.5 GW; with the 14.6 GW start-year fleet the grid-connected pathway reaches ~76 GW in 2038 vs the 11th Plan's 77.2 GW grid-connected figure. Self-consumption solar (plan: 12.2 GW in 2038) is carried separately in bldgs/BDESC.</t>
   </si>
 </sst>
 </file>
@@ -989,10 +1018,10 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1095,8 +1124,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCCCE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0EBD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2ECF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1403,6 +1447,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1411,7 +1483,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1558,9 +1630,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1619,6 +1688,20 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2011,6 +2094,9 @@
   <wetp:taskpane dockstate="right" visibility="0" width="676" row="7">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
 </wetp:taskpanes>
 </file>
 
@@ -2028,12 +2114,26 @@
 </we:webextension>
 </file>
 
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{DC791A64-E608-48F8-830A-FB9842AB254B}">
+  <we:reference id="11d7cf85-ae5a-43b8-bc58-1e1a151cce24" version="1.0.0.1" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="ko-KR" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;e5e7b61e-ecb1-4dac-a78e-7af26d9ba6d3&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412B3F4C-C052-4E1C-AAAD-A68F7E4EFB62}">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="67.140625" customWidth="1"/>
+    <col min="2" max="2" width="67.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2043,18 +2143,21 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="90" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>229</v>
+      </c>
       <c r="B4" s="5">
         <v>2025</v>
       </c>
@@ -2075,13 +2178,13 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="B9" s="91" t="s">
-        <v>207</v>
+      <c r="B9" s="90" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2090,16 +2193,16 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="B12" s="66" t="s">
-        <v>208</v>
+      <c r="B12" s="65" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="B13" s="66"/>
+      <c r="B13" s="65"/>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2112,860 +2215,919 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+    <row r="18" spans="1:2">
+      <c r="B18" s="90" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" s="65" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="2"/>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1">
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1" ht="16">
+      <c r="A33" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="16">
       <c r="A34" s="1"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" ht="16">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" ht="16">
       <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1" ht="16">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1" ht="16">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" ht="16">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" ht="16">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" ht="16">
+      <c r="A41" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B12" r:id="rId1" xr:uid="{E73DD173-2E66-4365-801D-D66565E27440}"/>
+    <hyperlink ref="B20" r:id="rId2" xr:uid="{481BBE92-2562-4404-998B-93C55D6DFDDB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA695273-2CF3-45E6-9FCD-C1FCC1300692}">
-  <dimension ref="A1:R111"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:R117"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="19.90625" customWidth="1"/>
+    <col min="3" max="3" width="18.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.36328125" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="82" customFormat="1" ht="15.75">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:18" s="81" customFormat="1" ht="15.5">
+      <c r="A1" s="80" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="9" customFormat="1" ht="20.149999999999999" customHeight="1">
+      <c r="A4" s="97" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="97" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="97" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="E4" s="98" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="98" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="98" t="s">
+        <v>157</v>
+      </c>
+      <c r="I4" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="J4" s="98" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="20.149999999999999" customHeight="1">
+      <c r="A5" s="99" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="101">
+        <v>12745.227000000001</v>
+      </c>
+      <c r="F5" s="101">
+        <v>17356.934000000001</v>
+      </c>
+      <c r="G5" s="101">
+        <v>21199.350999999999</v>
+      </c>
+      <c r="H5" s="101">
+        <v>24369.531999999999</v>
+      </c>
+      <c r="I5" s="101">
+        <v>28033.335999999999</v>
+      </c>
+      <c r="J5" s="101">
+        <v>32002.587</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="20.149999999999999" customHeight="1">
+      <c r="A6" s="100" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="100" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="101">
+        <v>10673.133</v>
+      </c>
+      <c r="F6" s="101">
+        <v>14910.941999999999</v>
+      </c>
+      <c r="G6" s="101">
+        <v>18338.404999999999</v>
+      </c>
+      <c r="H6" s="101">
+        <v>21051.253000000001</v>
+      </c>
+      <c r="I6" s="101">
+        <v>24186.093000000001</v>
+      </c>
+      <c r="J6" s="101">
+        <v>27382.319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="20.149999999999999" customHeight="1">
+      <c r="A7" s="100" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="100" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="99" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="101">
+        <v>2072.0940000000001</v>
+      </c>
+      <c r="F7" s="101">
+        <v>2445.9920000000002</v>
+      </c>
+      <c r="G7" s="101">
+        <v>2860.9459999999999</v>
+      </c>
+      <c r="H7" s="101">
+        <v>3318.279</v>
+      </c>
+      <c r="I7" s="101">
+        <v>3847.2420000000002</v>
+      </c>
+      <c r="J7" s="101">
+        <v>4620.268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102">
+        <f>F6-E6</f>
+        <v>4237.8089999999993</v>
+      </c>
+      <c r="G8" s="102">
+        <f t="shared" ref="G8:J8" si="0">G6-F6</f>
+        <v>3427.4629999999997</v>
+      </c>
+      <c r="H8" s="102">
+        <f t="shared" si="0"/>
+        <v>2712.8480000000018</v>
+      </c>
+      <c r="I8" s="102">
+        <f t="shared" si="0"/>
+        <v>3134.84</v>
+      </c>
+      <c r="J8" s="102">
+        <f t="shared" si="0"/>
+        <v>3196.2259999999987</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="96" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="96" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="96" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="96" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="96" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="96" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" s="96" t="s">
+        <v>151</v>
+      </c>
+      <c r="I10" s="96" t="s">
+        <v>152</v>
+      </c>
+      <c r="J10" s="96" t="s">
+        <v>153</v>
+      </c>
+      <c r="K10" s="96" t="s">
+        <v>154</v>
+      </c>
+      <c r="L10" s="96" t="s">
+        <v>155</v>
+      </c>
+      <c r="M10" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="N10" s="96" t="s">
+        <v>157</v>
+      </c>
+      <c r="O10" s="96" t="s">
+        <v>158</v>
+      </c>
+      <c r="P10" s="96" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q10" s="96" t="s">
+        <v>160</v>
+      </c>
+      <c r="R10" s="96" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="29">
+      <c r="A11" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>167</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="J11" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="K11" s="64" t="s">
+        <v>172</v>
+      </c>
+      <c r="L11" s="64" t="s">
+        <v>173</v>
+      </c>
+      <c r="M11" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="N11" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="O11" s="64" t="s">
+        <v>176</v>
+      </c>
+      <c r="P11" s="64" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q11" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="R11" s="64" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ref="L12:O12" si="1">L11-K11</f>
+        <v>4095.5200000000004</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="1"/>
+        <v>3956.1799999999985</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="1"/>
+        <v>2986.2900000000009</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="1"/>
+        <v>2745.380000000001</v>
+      </c>
+      <c r="P12">
+        <f>P11-O11</f>
+        <v>3366.6399999999994</v>
+      </c>
+      <c r="Q12">
+        <f>Q11-P11</f>
+        <v>3877.119999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>181</v>
+      </c>
+      <c r="L13" s="103"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="103"/>
+      <c r="O13" s="103"/>
+      <c r="P13" s="103"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="103"/>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>150</v>
-      </c>
-      <c r="H4" s="64" t="s">
-        <v>151</v>
-      </c>
-      <c r="I4" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="J4" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="K4" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="L4" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="M4" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="N4" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="O4" s="64" t="s">
-        <v>158</v>
-      </c>
-      <c r="P4" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q4" s="64" t="s">
-        <v>160</v>
-      </c>
-      <c r="R4" s="64" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="30">
-      <c r="A5" s="65" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" s="65" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>164</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="F5" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="G5" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="H5" s="65" t="s">
-        <v>169</v>
-      </c>
-      <c r="I5" s="65" t="s">
-        <v>170</v>
-      </c>
-      <c r="J5" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="K5" s="65" t="s">
-        <v>172</v>
-      </c>
-      <c r="L5" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="M5" s="65" t="s">
-        <v>174</v>
-      </c>
-      <c r="N5" s="65" t="s">
-        <v>175</v>
-      </c>
-      <c r="O5" s="65" t="s">
-        <v>176</v>
-      </c>
-      <c r="P5" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q5" s="65" t="s">
-        <v>178</v>
-      </c>
-      <c r="R5" s="65" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="66" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="58">
-        <v>222.5</v>
-      </c>
-      <c r="C11" s="59">
-        <v>2445.52</v>
-      </c>
-      <c r="D11" s="58">
-        <v>129</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="58">
-        <v>298.36</v>
-      </c>
-      <c r="C12" s="59">
-        <v>2268.23</v>
-      </c>
-      <c r="D12" s="58">
-        <v>127</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="58">
-        <v>169.3</v>
-      </c>
-      <c r="C13" s="59">
-        <v>1970.37</v>
-      </c>
-      <c r="D13" s="58">
-        <v>121</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="58">
-        <v>94.8</v>
-      </c>
-      <c r="C14" s="59">
-        <v>1803.47</v>
-      </c>
-      <c r="D14" s="58">
-        <v>115</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="58">
-        <v>63.6</v>
-      </c>
-      <c r="C15" s="59">
-        <v>1705.22</v>
-      </c>
-      <c r="D15" s="58">
-        <v>109</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="58">
+        <v>222.5</v>
+      </c>
+      <c r="C17" s="59">
+        <v>2445.52</v>
+      </c>
+      <c r="D17" s="58">
+        <v>129</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="58">
+        <v>298.36</v>
+      </c>
+      <c r="C18" s="59">
+        <v>2268.23</v>
+      </c>
+      <c r="D18" s="58">
+        <v>127</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="58">
+        <v>169.3</v>
+      </c>
+      <c r="C19" s="59">
+        <v>1970.37</v>
+      </c>
+      <c r="D19" s="58">
+        <v>121</v>
+      </c>
+      <c r="E19" s="57" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="58">
+        <v>94.8</v>
+      </c>
+      <c r="C20" s="59">
+        <v>1803.47</v>
+      </c>
+      <c r="D20" s="58">
+        <v>115</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="58">
+        <v>63.6</v>
+      </c>
+      <c r="C21" s="59">
+        <v>1705.22</v>
+      </c>
+      <c r="D21" s="58">
+        <v>109</v>
+      </c>
+      <c r="E21" s="57" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="58">
+      <c r="B22" s="58">
         <v>160.05000000000001</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C22" s="59">
         <v>1641.62</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D22" s="58">
         <v>106</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E22" s="57" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="57" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B23" s="58">
         <v>191.02500000000001</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C23" s="59">
         <v>1490.22</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D23" s="58">
         <v>103</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E23" s="57" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="62" t="s">
+    <row r="24" spans="1:5" ht="16">
+      <c r="A24" s="62" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="57" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B27" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C27" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D27" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="E21" s="60" t="s">
+      <c r="E27" s="60" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="57" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="59">
+      <c r="B28" s="59">
         <v>2081.39</v>
       </c>
-      <c r="C22" s="58">
+      <c r="C28" s="58">
         <v>364.13</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D28" s="59">
         <v>2445.52</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E28" s="61">
         <v>0.1489</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="57" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="59">
+      <c r="B29" s="59">
         <v>2007.4</v>
       </c>
-      <c r="C23" s="58">
+      <c r="C29" s="58">
         <v>260.83</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D29" s="59">
         <v>2268.23</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E29" s="61">
         <v>0.115</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="57" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="59">
+      <c r="B30" s="59">
         <v>1819.87</v>
       </c>
-      <c r="C24" s="58">
+      <c r="C30" s="58">
         <v>150.5</v>
       </c>
-      <c r="D24" s="59">
+      <c r="D30" s="59">
         <v>1970.37</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E30" s="61">
         <v>7.6399999999999996E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="57" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="59">
+      <c r="B31" s="59">
         <v>1678.97</v>
       </c>
-      <c r="C25" s="58">
+      <c r="C31" s="58">
         <v>124.5</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D31" s="59">
         <v>1803.47</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E31" s="61">
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="57" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="59">
+      <c r="B32" s="59">
         <v>1580.72</v>
       </c>
-      <c r="C26" s="58">
+      <c r="C32" s="58">
         <v>124.5</v>
       </c>
-      <c r="D26" s="59">
+      <c r="D32" s="59">
         <v>1705.22</v>
       </c>
-      <c r="E26" s="61">
+      <c r="E32" s="61">
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="57" t="s">
+    <row r="33" spans="1:13">
+      <c r="A33" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="59">
+      <c r="B33" s="59">
         <v>1517.12</v>
       </c>
-      <c r="C27" s="58">
+      <c r="C33" s="58">
         <v>124.5</v>
       </c>
-      <c r="D27" s="59">
+      <c r="D33" s="59">
         <v>1641.62</v>
       </c>
-      <c r="E27" s="61">
+      <c r="E33" s="61">
         <v>7.5800000000000006E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="57" t="s">
+    <row r="34" spans="1:13">
+      <c r="A34" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="59">
+      <c r="B34" s="59">
         <v>1425.72</v>
       </c>
-      <c r="C28" s="58">
+      <c r="C34" s="58">
         <v>64.5</v>
       </c>
-      <c r="D28" s="59">
+      <c r="D34" s="59">
         <v>1490.22</v>
       </c>
-      <c r="E28" s="61">
+      <c r="E34" s="61">
         <v>4.3299999999999998E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="84" t="s">
-        <v>201</v>
-      </c>
-      <c r="B30" s="85"/>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="86" t="s">
+    <row r="36" spans="1:13">
+      <c r="A36" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="84"/>
+      <c r="C36" s="84"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84"/>
+      <c r="J36" s="84"/>
+      <c r="K36" s="84"/>
+      <c r="L36" s="84"/>
+      <c r="M36" s="84"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="87" t="s">
+      <c r="B37" s="84"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="84"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="84"/>
+      <c r="M37" s="84"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="86" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" s="84"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="86" t="s">
         <v>196</v>
       </c>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="87" t="s">
+      <c r="B39" s="84"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="84"/>
+      <c r="K39" s="84"/>
+      <c r="L39" s="84"/>
+      <c r="M39" s="84"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="87" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" s="84"/>
+      <c r="C40" s="84"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="86" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="88" t="s">
-        <v>200</v>
-      </c>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="85"/>
-      <c r="L34" s="85"/>
-      <c r="M34" s="85"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="87" t="s">
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="86" t="s">
         <v>198</v>
       </c>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="85"/>
-      <c r="L35" s="85"/>
-      <c r="M35" s="85"/>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="87" t="s">
-        <v>199</v>
-      </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="85"/>
-      <c r="K36" s="85"/>
-      <c r="L36" s="85"/>
-      <c r="M36" s="85"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="63"/>
-    </row>
-    <row r="39" spans="1:13" s="83" customFormat="1" ht="15.75">
-      <c r="A39" s="81" t="s">
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
+      <c r="I42" s="84"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="63"/>
+    </row>
+    <row r="45" spans="1:13" s="82" customFormat="1" ht="15.5">
+      <c r="A45" s="80" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="63"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="72" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="63"/>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="73" t="s">
-        <v>194</v>
-      </c>
-      <c r="D42" s="7" t="s">
+      <c r="D48" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="7" t="s">
+    <row r="49" spans="1:10">
+      <c r="A49" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B49" s="7">
         <v>28150</v>
       </c>
-      <c r="C43" s="77">
+      <c r="C49" s="76">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!B10</f>
         <v>31964</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D49" s="7">
         <v>77203</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="7" t="s">
+    <row r="50" spans="1:10">
+      <c r="A50" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B50" s="7">
         <v>2293</v>
       </c>
-      <c r="C44" s="77">
+      <c r="C50" s="76">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!C10</f>
         <v>3017</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D50" s="7">
         <v>40671</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="7" t="s">
+    <row r="51" spans="1:10">
+      <c r="A51" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B51" s="7">
         <v>1852</v>
       </c>
-      <c r="C45" s="77">
+      <c r="C51" s="76">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!F10</f>
         <v>1852</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D51" s="7">
         <v>1852</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="63"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="63"/>
-      <c r="I47" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" s="7">
-        <v>2019</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2020</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2021</v>
-      </c>
-      <c r="E48" s="7">
-        <v>2022</v>
-      </c>
-      <c r="F48" s="7">
-        <v>2023</v>
-      </c>
-      <c r="G48" s="7">
-        <v>2024</v>
-      </c>
-      <c r="H48" s="7">
-        <v>2025</v>
-      </c>
-      <c r="I48" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="67">
-        <f>K5-0</f>
-        <v>8798.26</v>
-      </c>
-      <c r="C49" s="67">
-        <f>L5-0</f>
-        <v>12893.78</v>
-      </c>
-      <c r="D49" s="67">
-        <f t="shared" ref="D49:F49" si="0">M5-0</f>
-        <v>16849.96</v>
-      </c>
-      <c r="E49" s="67">
-        <f t="shared" si="0"/>
-        <v>19836.25</v>
-      </c>
-      <c r="F49" s="67">
-        <f t="shared" si="0"/>
-        <v>22581.63</v>
-      </c>
-      <c r="G49" s="75">
-        <f>B43</f>
-        <v>28150</v>
-      </c>
-      <c r="H49" s="75">
-        <f>C43</f>
-        <v>31964</v>
-      </c>
-      <c r="I49" s="68">
-        <v>31947.548449999998</v>
-      </c>
-      <c r="J49" s="74"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B50" s="67">
-        <f>B28</f>
-        <v>1425.72</v>
-      </c>
-      <c r="C50" s="67">
-        <f>B27</f>
-        <v>1517.12</v>
-      </c>
-      <c r="D50" s="67">
-        <f>B26</f>
-        <v>1580.72</v>
-      </c>
-      <c r="E50" s="67">
-        <f>B25</f>
-        <v>1678.97</v>
-      </c>
-      <c r="F50" s="67">
-        <f>B25</f>
-        <v>1678.97</v>
-      </c>
-      <c r="G50" s="67">
-        <f>B44-G51</f>
-        <v>2032.17</v>
-      </c>
-      <c r="H50" s="71">
-        <f>C44-H51</f>
-        <v>2652.87</v>
-      </c>
-      <c r="I50" s="68">
-        <v>2149.8716999999997</v>
-      </c>
-      <c r="J50" s="74"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" s="67">
-        <f>C28</f>
-        <v>64.5</v>
-      </c>
-      <c r="C51" s="67">
-        <f>C27</f>
-        <v>124.5</v>
-      </c>
-      <c r="D51" s="67">
-        <f>C26</f>
-        <v>124.5</v>
-      </c>
-      <c r="E51" s="67">
-        <f>C25</f>
-        <v>124.5</v>
-      </c>
-      <c r="F51" s="67">
-        <f>C24</f>
-        <v>150.5</v>
-      </c>
-      <c r="G51" s="67">
-        <f>C23</f>
-        <v>260.83</v>
-      </c>
-      <c r="H51" s="71">
-        <f>C22</f>
-        <v>364.13</v>
-      </c>
-      <c r="I51" s="68">
-        <v>320.60000000000002</v>
-      </c>
-      <c r="J51" s="74"/>
+    <row r="52" spans="1:10">
+      <c r="A52" s="63"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="63" t="s">
-        <v>185</v>
+      <c r="A53" s="63"/>
+      <c r="I53" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2993,409 +3155,555 @@
       <c r="H54" s="7">
         <v>2025</v>
       </c>
-      <c r="I54" s="69" t="s">
-        <v>186</v>
+      <c r="I54" s="7">
+        <v>2025</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B55" s="67">
-        <v>0</v>
-      </c>
-      <c r="C55" s="67">
-        <f>C49-B49</f>
-        <v>4095.5200000000004</v>
-      </c>
-      <c r="D55" s="67">
-        <f>D49-C49</f>
-        <v>3956.1799999999985</v>
-      </c>
-      <c r="E55" s="67">
-        <f t="shared" ref="E55:H55" si="1">E49-D49</f>
-        <v>2986.2900000000009</v>
-      </c>
-      <c r="F55" s="67">
-        <f t="shared" si="1"/>
-        <v>2745.380000000001</v>
-      </c>
-      <c r="G55" s="67">
-        <f t="shared" si="1"/>
-        <v>5568.369999999999</v>
-      </c>
-      <c r="H55" s="67">
-        <f t="shared" si="1"/>
-        <v>3814</v>
-      </c>
-      <c r="I55" s="70">
-        <f>SUM(C55:H55)</f>
-        <v>23165.739999999998</v>
-      </c>
+      <c r="B55" s="66">
+        <f>E6</f>
+        <v>10673.133</v>
+      </c>
+      <c r="C55" s="66">
+        <f t="shared" ref="C55:G55" si="2">F6</f>
+        <v>14910.941999999999</v>
+      </c>
+      <c r="D55" s="66">
+        <f t="shared" si="2"/>
+        <v>18338.404999999999</v>
+      </c>
+      <c r="E55" s="66">
+        <f t="shared" si="2"/>
+        <v>21051.253000000001</v>
+      </c>
+      <c r="F55" s="66">
+        <f t="shared" si="2"/>
+        <v>24186.093000000001</v>
+      </c>
+      <c r="G55" s="66">
+        <f t="shared" si="2"/>
+        <v>27382.319</v>
+      </c>
+      <c r="H55" s="66">
+        <f>C49</f>
+        <v>31964</v>
+      </c>
+      <c r="I55" s="67">
+        <v>31947.548449999998</v>
+      </c>
+      <c r="J55" s="73"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="67">
-        <v>0</v>
-      </c>
-      <c r="C56" s="67">
-        <f t="shared" ref="C56:C57" si="2">C50-B50</f>
-        <v>91.399999999999864</v>
-      </c>
-      <c r="D56" s="67">
-        <f t="shared" ref="D56:H57" si="3">D50-C50</f>
-        <v>63.600000000000136</v>
-      </c>
-      <c r="E56" s="67">
-        <f t="shared" si="3"/>
-        <v>98.25</v>
-      </c>
-      <c r="F56" s="67">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G56" s="67">
-        <f t="shared" si="3"/>
-        <v>353.20000000000005</v>
-      </c>
-      <c r="H56" s="67">
-        <f t="shared" si="3"/>
-        <v>620.69999999999982</v>
-      </c>
-      <c r="I56" s="70">
-        <f>SUM(C56:H56)</f>
-        <v>1227.1499999999999</v>
-      </c>
+      <c r="B56" s="66">
+        <f>B34</f>
+        <v>1425.72</v>
+      </c>
+      <c r="C56" s="66">
+        <f>B33</f>
+        <v>1517.12</v>
+      </c>
+      <c r="D56" s="66">
+        <f>B32</f>
+        <v>1580.72</v>
+      </c>
+      <c r="E56" s="66">
+        <f>B31</f>
+        <v>1678.97</v>
+      </c>
+      <c r="F56" s="66">
+        <f>B31</f>
+        <v>1678.97</v>
+      </c>
+      <c r="G56" s="66">
+        <f>B50-G57</f>
+        <v>2032.17</v>
+      </c>
+      <c r="H56" s="70">
+        <f>C50-H57</f>
+        <v>2652.87</v>
+      </c>
+      <c r="I56" s="67">
+        <v>2149.8716999999997</v>
+      </c>
+      <c r="J56" s="73"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B57" s="67">
-        <v>0</v>
-      </c>
-      <c r="C57" s="67">
-        <f t="shared" si="2"/>
+      <c r="B57" s="66">
+        <f>C34</f>
+        <v>64.5</v>
+      </c>
+      <c r="C57" s="66">
+        <f>C33</f>
+        <v>124.5</v>
+      </c>
+      <c r="D57" s="66">
+        <f>C32</f>
+        <v>124.5</v>
+      </c>
+      <c r="E57" s="66">
+        <f>C31</f>
+        <v>124.5</v>
+      </c>
+      <c r="F57" s="66">
+        <f>C30</f>
+        <v>150.5</v>
+      </c>
+      <c r="G57" s="66">
+        <f>C29</f>
+        <v>260.83</v>
+      </c>
+      <c r="H57" s="70">
+        <f>C28</f>
+        <v>364.13</v>
+      </c>
+      <c r="I57" s="67">
+        <v>320.60000000000002</v>
+      </c>
+      <c r="J57" s="73"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="63" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="7">
+        <v>2019</v>
+      </c>
+      <c r="C60" s="7">
+        <v>2020</v>
+      </c>
+      <c r="D60" s="7">
+        <v>2021</v>
+      </c>
+      <c r="E60" s="7">
+        <v>2022</v>
+      </c>
+      <c r="F60" s="7">
+        <v>2023</v>
+      </c>
+      <c r="G60" s="7">
+        <v>2024</v>
+      </c>
+      <c r="H60" s="7">
+        <v>2025</v>
+      </c>
+      <c r="I60" s="68" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="66">
+        <v>0</v>
+      </c>
+      <c r="C61" s="66">
+        <f>C55-B55</f>
+        <v>4237.8089999999993</v>
+      </c>
+      <c r="D61" s="66">
+        <f t="shared" ref="D61:G61" si="3">D55-C55</f>
+        <v>3427.4629999999997</v>
+      </c>
+      <c r="E61" s="66">
+        <f t="shared" si="3"/>
+        <v>2712.8480000000018</v>
+      </c>
+      <c r="F61" s="66">
+        <f t="shared" si="3"/>
+        <v>3134.84</v>
+      </c>
+      <c r="G61" s="66">
+        <f t="shared" si="3"/>
+        <v>3196.2259999999987</v>
+      </c>
+      <c r="H61" s="74">
+        <f>C49-B49</f>
+        <v>3814</v>
+      </c>
+      <c r="I61" s="69">
+        <f>SUM(C61:H61)</f>
+        <v>20523.186000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="66">
+        <v>0</v>
+      </c>
+      <c r="C62" s="66">
+        <f t="shared" ref="C62:C63" si="4">C56-B56</f>
+        <v>91.399999999999864</v>
+      </c>
+      <c r="D62" s="66">
+        <f t="shared" ref="D62:H63" si="5">D56-C56</f>
+        <v>63.600000000000136</v>
+      </c>
+      <c r="E62" s="66">
+        <f t="shared" si="5"/>
+        <v>98.25</v>
+      </c>
+      <c r="F62" s="66">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="66">
+        <f t="shared" si="5"/>
+        <v>353.20000000000005</v>
+      </c>
+      <c r="H62" s="66">
+        <f t="shared" si="5"/>
+        <v>620.69999999999982</v>
+      </c>
+      <c r="I62" s="69">
+        <f>SUM(C62:H62)</f>
+        <v>1227.1499999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="66">
+        <v>0</v>
+      </c>
+      <c r="C63" s="66">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="D57" s="67">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E57" s="67">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="67">
-        <f t="shared" si="3"/>
+      <c r="D63" s="66">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E63" s="66">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="66">
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="G57" s="67">
-        <f t="shared" si="3"/>
+      <c r="G63" s="66">
+        <f t="shared" si="5"/>
         <v>110.32999999999998</v>
       </c>
-      <c r="H57" s="67">
-        <f t="shared" si="3"/>
+      <c r="H63" s="66">
+        <f t="shared" si="5"/>
         <v>103.30000000000001</v>
       </c>
-      <c r="I57" s="70">
-        <f>SUM(C57:H57)</f>
+      <c r="I63" s="69">
+        <f>SUM(C63:H63)</f>
         <v>299.63</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17">
-      <c r="A103" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17">
-      <c r="A104" s="92" t="s">
-        <v>212</v>
-      </c>
-      <c r="B104" s="93">
-        <v>2023</v>
-      </c>
-      <c r="C104" s="93">
-        <v>2024</v>
-      </c>
-      <c r="D104" s="93">
-        <v>2025</v>
-      </c>
-      <c r="E104" s="93">
-        <v>2026</v>
-      </c>
-      <c r="F104" s="93">
-        <v>2027</v>
-      </c>
-      <c r="G104" s="93">
-        <v>2028</v>
-      </c>
-      <c r="H104" s="93">
-        <v>2029</v>
-      </c>
-      <c r="I104" s="93">
-        <v>2030</v>
-      </c>
-      <c r="J104" s="93">
-        <v>2031</v>
-      </c>
-      <c r="K104" s="93">
-        <v>2032</v>
-      </c>
-      <c r="L104" s="93">
-        <v>2033</v>
-      </c>
-      <c r="M104" s="93">
-        <v>2034</v>
-      </c>
-      <c r="N104" s="93">
-        <v>2035</v>
-      </c>
-      <c r="O104" s="93">
-        <v>2036</v>
-      </c>
-      <c r="P104" s="93">
-        <v>2037</v>
-      </c>
-      <c r="Q104" s="93">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17">
-      <c r="A105" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B105" s="13">
-        <v>561</v>
-      </c>
-      <c r="C105" s="13">
-        <v>887</v>
-      </c>
-      <c r="D105" s="13">
-        <v>946</v>
-      </c>
-      <c r="E105" s="13">
-        <v>1016</v>
-      </c>
-      <c r="F105" s="13">
-        <v>1088</v>
-      </c>
-      <c r="G105" s="13">
-        <v>1137</v>
-      </c>
-      <c r="H105" s="13">
-        <v>1172</v>
-      </c>
-      <c r="I105" s="13">
-        <v>1220</v>
-      </c>
-      <c r="J105" s="13">
-        <v>1256</v>
-      </c>
-      <c r="K105" s="13">
-        <v>1285</v>
-      </c>
-      <c r="L105" s="13">
-        <v>1310</v>
-      </c>
-      <c r="M105" s="13">
-        <v>1333</v>
-      </c>
-      <c r="N105" s="13">
-        <v>1360</v>
-      </c>
-      <c r="O105" s="13">
-        <v>1389</v>
-      </c>
-      <c r="P105" s="13">
-        <v>1416</v>
-      </c>
-      <c r="Q105" s="13">
-        <v>1445</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17">
-      <c r="A106" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B106" s="13">
-        <v>419</v>
-      </c>
-      <c r="C106" s="13">
-        <v>425</v>
-      </c>
-      <c r="D106" s="13">
-        <v>497</v>
-      </c>
-      <c r="E106" s="13">
-        <v>557</v>
-      </c>
-      <c r="F106" s="13">
-        <v>616</v>
-      </c>
-      <c r="G106" s="13">
-        <v>698</v>
-      </c>
-      <c r="H106" s="13">
-        <v>794</v>
-      </c>
-      <c r="I106" s="13">
-        <v>877</v>
-      </c>
-      <c r="J106" s="13">
-        <v>967</v>
-      </c>
-      <c r="K106" s="13">
-        <v>1065</v>
-      </c>
-      <c r="L106" s="13">
-        <v>1166</v>
-      </c>
-      <c r="M106" s="13">
-        <v>1270</v>
-      </c>
-      <c r="N106" s="13">
-        <v>1369</v>
-      </c>
-      <c r="O106" s="13">
-        <v>1466</v>
-      </c>
-      <c r="P106" s="13">
-        <v>1565</v>
-      </c>
-      <c r="Q106" s="13">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17">
-      <c r="A107" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B107" s="94">
-        <f>B105+B106</f>
-        <v>980</v>
-      </c>
-      <c r="C107" s="94">
-        <f t="shared" ref="C107:Q107" si="4">C105+C106</f>
-        <v>1312</v>
-      </c>
-      <c r="D107" s="94">
-        <f t="shared" si="4"/>
-        <v>1443</v>
-      </c>
-      <c r="E107" s="94">
-        <v>1574</v>
-      </c>
-      <c r="F107" s="94">
-        <f t="shared" si="4"/>
-        <v>1704</v>
-      </c>
-      <c r="G107" s="94">
-        <f t="shared" si="4"/>
-        <v>1835</v>
-      </c>
-      <c r="H107" s="94">
-        <f t="shared" si="4"/>
-        <v>1966</v>
-      </c>
-      <c r="I107" s="94">
-        <f t="shared" si="4"/>
-        <v>2097</v>
-      </c>
-      <c r="J107" s="94">
-        <f t="shared" si="4"/>
-        <v>2223</v>
-      </c>
-      <c r="K107" s="94">
-        <f t="shared" si="4"/>
-        <v>2350</v>
-      </c>
-      <c r="L107" s="94">
-        <f t="shared" si="4"/>
-        <v>2476</v>
-      </c>
-      <c r="M107" s="94">
-        <v>2602</v>
-      </c>
-      <c r="N107" s="94">
-        <f t="shared" si="4"/>
-        <v>2729</v>
-      </c>
-      <c r="O107" s="94">
-        <f t="shared" si="4"/>
-        <v>2855</v>
-      </c>
-      <c r="P107" s="94">
-        <v>2982</v>
-      </c>
-      <c r="Q107" s="94">
-        <f t="shared" si="4"/>
-        <v>3108</v>
       </c>
     </row>
     <row r="109" spans="1:17">
       <c r="A109" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110" spans="1:17">
-      <c r="A110" s="92" t="s">
-        <v>212</v>
-      </c>
-      <c r="B110" s="92" t="s">
-        <v>97</v>
-      </c>
-      <c r="C110" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="D110" s="92" t="s">
-        <v>214</v>
-      </c>
-      <c r="E110" s="92" t="s">
-        <v>112</v>
-      </c>
-      <c r="F110" s="92" t="s">
-        <v>95</v>
-      </c>
-      <c r="G110" s="92" t="s">
-        <v>215</v>
-      </c>
-      <c r="H110" s="92" t="s">
-        <v>101</v>
+      <c r="A110" s="91" t="s">
+        <v>211</v>
+      </c>
+      <c r="B110" s="92">
+        <v>2023</v>
+      </c>
+      <c r="C110" s="92">
+        <v>2024</v>
+      </c>
+      <c r="D110" s="92">
+        <v>2025</v>
+      </c>
+      <c r="E110" s="92">
+        <v>2026</v>
+      </c>
+      <c r="F110" s="92">
+        <v>2027</v>
+      </c>
+      <c r="G110" s="92">
+        <v>2028</v>
+      </c>
+      <c r="H110" s="92">
+        <v>2029</v>
+      </c>
+      <c r="I110" s="92">
+        <v>2030</v>
+      </c>
+      <c r="J110" s="92">
+        <v>2031</v>
+      </c>
+      <c r="K110" s="92">
+        <v>2032</v>
+      </c>
+      <c r="L110" s="92">
+        <v>2033</v>
+      </c>
+      <c r="M110" s="92">
+        <v>2034</v>
+      </c>
+      <c r="N110" s="92">
+        <v>2035</v>
+      </c>
+      <c r="O110" s="92">
+        <v>2036</v>
+      </c>
+      <c r="P110" s="92">
+        <v>2037</v>
+      </c>
+      <c r="Q110" s="92">
+        <v>2038</v>
       </c>
     </row>
     <row r="111" spans="1:17">
       <c r="A111" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B111" s="95">
-        <v>0</v>
-      </c>
-      <c r="C111" s="95">
+        <v>97</v>
+      </c>
+      <c r="B111" s="13">
+        <v>561</v>
+      </c>
+      <c r="C111" s="13">
+        <v>887</v>
+      </c>
+      <c r="D111" s="13">
+        <v>946</v>
+      </c>
+      <c r="E111" s="13">
+        <v>1016</v>
+      </c>
+      <c r="F111" s="13">
+        <v>1088</v>
+      </c>
+      <c r="G111" s="13">
+        <v>1137</v>
+      </c>
+      <c r="H111" s="13">
+        <v>1172</v>
+      </c>
+      <c r="I111" s="13">
+        <v>1220</v>
+      </c>
+      <c r="J111" s="13">
+        <v>1256</v>
+      </c>
+      <c r="K111" s="13">
+        <v>1285</v>
+      </c>
+      <c r="L111" s="13">
+        <v>1310</v>
+      </c>
+      <c r="M111" s="13">
+        <v>1333</v>
+      </c>
+      <c r="N111" s="13">
+        <v>1360</v>
+      </c>
+      <c r="O111" s="13">
+        <v>1389</v>
+      </c>
+      <c r="P111" s="13">
+        <v>1416</v>
+      </c>
+      <c r="Q111" s="13">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17">
+      <c r="A112" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B112" s="13">
+        <v>419</v>
+      </c>
+      <c r="C112" s="13">
+        <v>425</v>
+      </c>
+      <c r="D112" s="13">
+        <v>497</v>
+      </c>
+      <c r="E112" s="13">
+        <v>557</v>
+      </c>
+      <c r="F112" s="13">
+        <v>616</v>
+      </c>
+      <c r="G112" s="13">
+        <v>698</v>
+      </c>
+      <c r="H112" s="13">
+        <v>794</v>
+      </c>
+      <c r="I112" s="13">
+        <v>877</v>
+      </c>
+      <c r="J112" s="13">
+        <v>967</v>
+      </c>
+      <c r="K112" s="13">
+        <v>1065</v>
+      </c>
+      <c r="L112" s="13">
+        <v>1166</v>
+      </c>
+      <c r="M112" s="13">
+        <v>1270</v>
+      </c>
+      <c r="N112" s="13">
+        <v>1369</v>
+      </c>
+      <c r="O112" s="13">
+        <v>1466</v>
+      </c>
+      <c r="P112" s="13">
+        <v>1565</v>
+      </c>
+      <c r="Q112" s="13">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17">
+      <c r="A113" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B113" s="93">
+        <f>B111+B112</f>
+        <v>980</v>
+      </c>
+      <c r="C113" s="93">
+        <f t="shared" ref="C113:Q113" si="6">C111+C112</f>
+        <v>1312</v>
+      </c>
+      <c r="D113" s="93">
+        <f t="shared" si="6"/>
+        <v>1443</v>
+      </c>
+      <c r="E113" s="93">
+        <v>1574</v>
+      </c>
+      <c r="F113" s="93">
+        <f t="shared" si="6"/>
+        <v>1704</v>
+      </c>
+      <c r="G113" s="93">
+        <f t="shared" si="6"/>
+        <v>1835</v>
+      </c>
+      <c r="H113" s="93">
+        <f t="shared" si="6"/>
+        <v>1966</v>
+      </c>
+      <c r="I113" s="93">
+        <f t="shared" si="6"/>
+        <v>2097</v>
+      </c>
+      <c r="J113" s="93">
+        <f t="shared" si="6"/>
+        <v>2223</v>
+      </c>
+      <c r="K113" s="93">
+        <f t="shared" si="6"/>
+        <v>2350</v>
+      </c>
+      <c r="L113" s="93">
+        <f t="shared" si="6"/>
+        <v>2476</v>
+      </c>
+      <c r="M113" s="93">
+        <v>2602</v>
+      </c>
+      <c r="N113" s="93">
+        <f t="shared" si="6"/>
+        <v>2729</v>
+      </c>
+      <c r="O113" s="93">
+        <f t="shared" si="6"/>
+        <v>2855</v>
+      </c>
+      <c r="P113" s="93">
+        <v>2982</v>
+      </c>
+      <c r="Q113" s="93">
+        <f t="shared" si="6"/>
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17">
+      <c r="A115" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17">
+      <c r="A116" s="91" t="s">
+        <v>211</v>
+      </c>
+      <c r="B116" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C116" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="D116" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="E116" s="91" t="s">
+        <v>112</v>
+      </c>
+      <c r="F116" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="G116" s="91" t="s">
+        <v>214</v>
+      </c>
+      <c r="H116" s="91" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17">
+      <c r="A117" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B117" s="94">
+        <v>0</v>
+      </c>
+      <c r="C117" s="94">
         <v>0.3</v>
       </c>
-      <c r="D111" s="95">
+      <c r="D117" s="94">
         <v>27.7</v>
       </c>
-      <c r="E111" s="95">
+      <c r="E117" s="94">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F111" s="95">
-        <v>0</v>
-      </c>
-      <c r="G111" s="95">
+      <c r="F117" s="94">
+        <v>0</v>
+      </c>
+      <c r="G117" s="94">
         <v>32.1</v>
       </c>
-      <c r="H111" s="95">
+      <c r="H117" s="94">
         <v>73.2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="https://recloud.energy.or.kr/present/sub3_2_2.do" xr:uid="{D230838C-6DA4-4C20-9591-56B039745110}"/>
+    <hyperlink ref="A12" r:id="rId1" display="https://recloud.energy.or.kr/present/sub3_2_2.do" xr:uid="{D230838C-6DA4-4C20-9591-56B039745110}"/>
+    <hyperlink ref="A8" r:id="rId2" xr:uid="{703990B3-775F-4A3F-B605-EF1B30BE5D60}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3404,14 +3712,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989B43D5-5E80-4E96-A0E6-9AF45A7C32E3}">
   <dimension ref="A2:J48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.90625" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
@@ -3734,7 +4042,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D25" s="96">
+      <c r="D25" s="95">
         <f t="shared" si="0"/>
         <v>3098</v>
       </c>
@@ -3879,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -3887,31 +4195,31 @@
         <v>13</v>
       </c>
       <c r="B30" s="7">
-        <f>'재생에너지설비현황_19~25'!B56</f>
+        <f>'재생에너지설비현황_19~25'!B62</f>
         <v>0</v>
       </c>
       <c r="C30" s="7">
-        <f>'재생에너지설비현황_19~25'!C56</f>
+        <f>'재생에너지설비현황_19~25'!C62</f>
         <v>91.399999999999864</v>
       </c>
       <c r="D30" s="7">
-        <f>'재생에너지설비현황_19~25'!D56</f>
+        <f>'재생에너지설비현황_19~25'!D62</f>
         <v>63.600000000000136</v>
       </c>
       <c r="E30" s="7">
-        <f>'재생에너지설비현황_19~25'!E56</f>
+        <f>'재생에너지설비현황_19~25'!E62</f>
         <v>98.25</v>
       </c>
       <c r="F30" s="7">
-        <f>'재생에너지설비현황_19~25'!F56</f>
+        <f>'재생에너지설비현황_19~25'!F62</f>
         <v>0</v>
       </c>
       <c r="G30" s="7">
-        <f>'재생에너지설비현황_19~25'!G56</f>
+        <f>'재생에너지설비현황_19~25'!G62</f>
         <v>353.20000000000005</v>
       </c>
       <c r="H30" s="7">
-        <f>'재생에너지설비현황_19~25'!H56</f>
+        <f>'재생에너지설비현황_19~25'!H62</f>
         <v>620.69999999999982</v>
       </c>
     </row>
@@ -3920,31 +4228,31 @@
         <v>12</v>
       </c>
       <c r="B31" s="7">
-        <f>'재생에너지설비현황_19~25'!B55</f>
+        <f>'재생에너지설비현황_19~25'!B61</f>
         <v>0</v>
       </c>
       <c r="C31" s="7">
-        <f>'재생에너지설비현황_19~25'!C55</f>
-        <v>4095.5200000000004</v>
+        <f>'재생에너지설비현황_19~25'!C61</f>
+        <v>4237.8089999999993</v>
       </c>
       <c r="D31" s="7">
-        <f>'재생에너지설비현황_19~25'!D55</f>
-        <v>3956.1799999999985</v>
+        <f>'재생에너지설비현황_19~25'!D61</f>
+        <v>3427.4629999999997</v>
       </c>
       <c r="E31" s="7">
-        <f>'재생에너지설비현황_19~25'!E55</f>
-        <v>2986.2900000000009</v>
+        <f>'재생에너지설비현황_19~25'!E61</f>
+        <v>2712.8480000000018</v>
       </c>
       <c r="F31" s="7">
-        <f>'재생에너지설비현황_19~25'!F55</f>
-        <v>2745.380000000001</v>
+        <f>'재생에너지설비현황_19~25'!F61</f>
+        <v>3134.84</v>
       </c>
       <c r="G31" s="7">
-        <f>'재생에너지설비현황_19~25'!G55</f>
-        <v>5568.369999999999</v>
+        <f>'재생에너지설비현황_19~25'!G61</f>
+        <v>3196.2259999999987</v>
       </c>
       <c r="H31" s="7">
-        <f>'재생에너지설비현황_19~25'!H55</f>
+        <f>'재생에너지설비현황_19~25'!H61</f>
         <v>3814</v>
       </c>
     </row>
@@ -4109,31 +4417,31 @@
         <v>14</v>
       </c>
       <c r="B38" s="7">
-        <f>'재생에너지설비현황_19~25'!B57</f>
+        <f>'재생에너지설비현황_19~25'!B63</f>
         <v>0</v>
       </c>
       <c r="C38" s="7">
-        <f>'재생에너지설비현황_19~25'!C57</f>
+        <f>'재생에너지설비현황_19~25'!C63</f>
         <v>60</v>
       </c>
       <c r="D38" s="7">
-        <f>'재생에너지설비현황_19~25'!D57</f>
+        <f>'재생에너지설비현황_19~25'!D63</f>
         <v>0</v>
       </c>
       <c r="E38" s="7">
-        <f>'재생에너지설비현황_19~25'!E57</f>
+        <f>'재생에너지설비현황_19~25'!E63</f>
         <v>0</v>
       </c>
       <c r="F38" s="7">
-        <f>'재생에너지설비현황_19~25'!F57</f>
+        <f>'재생에너지설비현황_19~25'!F63</f>
         <v>26</v>
       </c>
       <c r="G38" s="7">
-        <f>'재생에너지설비현황_19~25'!G57</f>
+        <f>'재생에너지설비현황_19~25'!G63</f>
         <v>110.32999999999998</v>
       </c>
       <c r="H38" s="7">
-        <f>'재생에너지설비현황_19~25'!H57</f>
+        <f>'재생에너지설비현황_19~25'!H63</f>
         <v>103.30000000000001</v>
       </c>
     </row>
@@ -4406,15 +4714,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA04839C-7E1C-4865-9899-1ED4BC37516C}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
-    <col min="2" max="13" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" customWidth="1"/>
+    <col min="2" max="13" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="83" customFormat="1" ht="15.75">
-      <c r="A1" s="81" t="s">
-        <v>204</v>
+    <row r="1" spans="1:13" s="82" customFormat="1" ht="15.5">
+      <c r="A1" s="80" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4451,7 +4759,7 @@
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
     </row>
-    <row r="4" spans="1:13" ht="15.75" thickBot="1">
+    <row r="4" spans="1:13" ht="15" thickBot="1">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -4469,51 +4777,51 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="99" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="102" t="s">
+      <c r="A5" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="109" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102" t="s">
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="M5" s="105" t="s">
+      <c r="M5" s="112" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="100"/>
-      <c r="B6" s="103" t="s">
+      <c r="A6" s="107"/>
+      <c r="B6" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103" t="s">
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103" t="s">
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="L6" s="103"/>
-      <c r="M6" s="106"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A7" s="101"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="113"/>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1">
+      <c r="A7" s="108"/>
       <c r="B7" s="24" t="s">
         <v>97</v>
       </c>
@@ -4541,12 +4849,12 @@
       <c r="J7" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="107"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="114"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="108">
+      <c r="A8" s="115">
         <v>2024</v>
       </c>
       <c r="B8" s="22">
@@ -4587,7 +4895,7 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="97"/>
+      <c r="A9" s="104"/>
       <c r="B9" s="17">
         <v>4025</v>
       </c>
@@ -4622,7 +4930,7 @@
       <c r="M9" s="20"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="97">
+      <c r="A10" s="104">
         <v>2025</v>
       </c>
       <c r="B10" s="16">
@@ -4663,7 +4971,7 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="97"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="17">
         <v>4571</v>
       </c>
@@ -4698,7 +5006,7 @@
       <c r="M11" s="20"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="97">
+      <c r="A12" s="104">
         <v>2026</v>
       </c>
       <c r="B12" s="16">
@@ -4739,7 +5047,7 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="97"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="17">
         <v>5161</v>
       </c>
@@ -4774,7 +5082,7 @@
       <c r="M13" s="20"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="97">
+      <c r="A14" s="104">
         <v>2027</v>
       </c>
       <c r="B14" s="16">
@@ -4815,7 +5123,7 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="97"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="17">
         <v>5780</v>
       </c>
@@ -4850,7 +5158,7 @@
       <c r="M15" s="20"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="97">
+      <c r="A16" s="104">
         <v>2028</v>
       </c>
       <c r="B16" s="16">
@@ -4891,7 +5199,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="97"/>
+      <c r="A17" s="104"/>
       <c r="B17" s="17">
         <v>6409</v>
       </c>
@@ -4926,7 +5234,7 @@
       <c r="M17" s="20"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="97">
+      <c r="A18" s="104">
         <v>2029</v>
       </c>
       <c r="B18" s="16">
@@ -4967,7 +5275,7 @@
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="97"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="17">
         <v>7046</v>
       </c>
@@ -5002,7 +5310,7 @@
       <c r="M19" s="20"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="97">
+      <c r="A20" s="104">
         <v>2030</v>
       </c>
       <c r="B20" s="16">
@@ -5043,7 +5351,7 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="97"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="17">
         <v>7962</v>
       </c>
@@ -5078,7 +5386,7 @@
       <c r="M21" s="20"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="97">
+      <c r="A22" s="104">
         <v>2031</v>
       </c>
       <c r="B22" s="16">
@@ -5119,7 +5427,7 @@
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="97"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="17">
         <v>8396</v>
       </c>
@@ -5154,7 +5462,7 @@
       <c r="M23" s="20"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="97">
+      <c r="A24" s="104">
         <v>2032</v>
       </c>
       <c r="B24" s="16">
@@ -5195,7 +5503,7 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="97"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="17">
         <v>8829</v>
       </c>
@@ -5230,7 +5538,7 @@
       <c r="M25" s="20"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="97">
+      <c r="A26" s="104">
         <v>2033</v>
       </c>
       <c r="B26" s="16">
@@ -5271,7 +5579,7 @@
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="97"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="17">
         <v>9261</v>
       </c>
@@ -5306,7 +5614,7 @@
       <c r="M27" s="20"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="97">
+      <c r="A28" s="104">
         <v>2034</v>
       </c>
       <c r="B28" s="16">
@@ -5347,7 +5655,7 @@
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="97"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="17">
         <v>9693</v>
       </c>
@@ -5382,7 +5690,7 @@
       <c r="M29" s="20"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="97">
+      <c r="A30" s="104">
         <v>2035</v>
       </c>
       <c r="B30" s="16">
@@ -5423,7 +5731,7 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="97"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="17">
         <v>10126</v>
       </c>
@@ -5458,7 +5766,7 @@
       <c r="M31" s="20"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="97">
+      <c r="A32" s="104">
         <v>2036</v>
       </c>
       <c r="B32" s="16">
@@ -5499,7 +5807,7 @@
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="97"/>
+      <c r="A33" s="104"/>
       <c r="B33" s="17">
         <v>10431</v>
       </c>
@@ -5534,7 +5842,7 @@
       <c r="M33" s="20"/>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" s="97">
+      <c r="A34" s="104">
         <v>2037</v>
       </c>
       <c r="B34" s="16">
@@ -5575,7 +5883,7 @@
       </c>
     </row>
     <row r="35" spans="1:17">
-      <c r="A35" s="97"/>
+      <c r="A35" s="104"/>
       <c r="B35" s="17">
         <v>10735</v>
       </c>
@@ -5610,7 +5918,7 @@
       <c r="M35" s="20"/>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="97">
+      <c r="A36" s="104">
         <v>2038</v>
       </c>
       <c r="B36" s="16">
@@ -5650,8 +5958,8 @@
         <v>138068</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A37" s="98"/>
+    <row r="37" spans="1:17" ht="15" thickBot="1">
+      <c r="A37" s="105"/>
       <c r="B37" s="18">
         <v>11040</v>
       </c>
@@ -5702,13 +6010,13 @@
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="42" spans="1:17" s="83" customFormat="1" ht="15.75">
-      <c r="A42" s="81" t="s">
+    <row r="42" spans="1:17" s="82" customFormat="1" ht="15.5">
+      <c r="A42" s="80" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" thickBot="1"/>
-    <row r="44" spans="1:17" ht="15.75" thickBot="1">
+    <row r="43" spans="1:17" ht="15" thickBot="1"/>
+    <row r="44" spans="1:17" ht="15" thickBot="1">
       <c r="A44" s="46" t="s">
         <v>80</v>
       </c>
@@ -6087,7 +6395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="15.75" thickBot="1">
+    <row r="50" spans="1:16" ht="15" thickBot="1">
       <c r="A50" s="40" t="s">
         <v>121</v>
       </c>
@@ -6148,17 +6456,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="83" customFormat="1" ht="15.75">
-      <c r="A52" s="81" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="15.75" thickBot="1">
+    <row r="52" spans="1:16" s="82" customFormat="1" ht="15.5">
+      <c r="A52" s="80" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15" thickBot="1">
       <c r="A53" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15.75" thickBot="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" thickBot="1">
       <c r="A54" s="46" t="s">
         <v>80</v>
       </c>
@@ -6207,7 +6515,7 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B55" s="44"/>
       <c r="C55" s="44">
@@ -6265,7 +6573,7 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B56" s="35"/>
       <c r="C56" s="44">
@@ -6323,122 +6631,122 @@
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B57" s="78">
+        <v>191</v>
+      </c>
+      <c r="B57" s="77">
         <f>C10</f>
         <v>3017</v>
       </c>
-      <c r="C57" s="72">
+      <c r="C57" s="71">
         <f>C12</f>
         <v>3958</v>
       </c>
-      <c r="D57" s="72">
+      <c r="D57" s="71">
         <f>C14</f>
         <v>5983</v>
       </c>
-      <c r="E57" s="72">
+      <c r="E57" s="71">
         <f>C16</f>
         <v>8719</v>
       </c>
-      <c r="F57" s="72">
+      <c r="F57" s="71">
         <f>C18</f>
         <v>14661</v>
       </c>
-      <c r="G57" s="78">
+      <c r="G57" s="77">
         <f>C20</f>
         <v>18281</v>
       </c>
-      <c r="H57" s="72">
+      <c r="H57" s="71">
         <f>C22</f>
         <v>22321</v>
       </c>
-      <c r="I57" s="72">
+      <c r="I57" s="71">
         <f>C24</f>
         <v>24868</v>
       </c>
-      <c r="J57" s="72">
+      <c r="J57" s="71">
         <f>C26</f>
         <v>27419</v>
       </c>
-      <c r="K57" s="72">
+      <c r="K57" s="71">
         <f>C28</f>
         <v>29973</v>
       </c>
-      <c r="L57" s="72">
+      <c r="L57" s="71">
         <f>C30</f>
         <v>32972</v>
       </c>
-      <c r="M57" s="72">
+      <c r="M57" s="71">
         <f>C32</f>
         <v>35532</v>
       </c>
-      <c r="N57" s="72">
+      <c r="N57" s="71">
         <f>C34</f>
         <v>38101</v>
       </c>
-      <c r="O57" s="72">
+      <c r="O57" s="71">
         <f>C36</f>
         <v>40671</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B58" s="79">
-        <f>'재생에너지설비현황_19~25'!I56</f>
+        <v>189</v>
+      </c>
+      <c r="B58" s="78">
+        <f>'재생에너지설비현황_19~25'!I62</f>
         <v>1227.1499999999999</v>
       </c>
-      <c r="C58" s="72">
+      <c r="C58" s="71">
         <f>_xlfn.FORECAST.LINEAR(C$54, CHOOSE({1,2},$B58,$G58),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>1777.9199999999255</v>
       </c>
-      <c r="D58" s="72">
+      <c r="D58" s="71">
         <f>_xlfn.FORECAST.LINEAR(D$54, CHOOSE({1,2},$B58,$G58),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>2328.6899999999441</v>
       </c>
-      <c r="E58" s="72">
+      <c r="E58" s="71">
         <f>_xlfn.FORECAST.LINEAR(E$54, CHOOSE({1,2},$B58,$G58),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>2879.4599999999627</v>
       </c>
-      <c r="F58" s="72">
+      <c r="F58" s="71">
         <f>_xlfn.FORECAST.LINEAR(F$54, CHOOSE({1,2},$B58,$G58),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>3430.2299999999814</v>
       </c>
-      <c r="G58" s="78">
+      <c r="G58" s="77">
         <f>G57-G59</f>
         <v>3981</v>
       </c>
-      <c r="H58" s="72">
+      <c r="H58" s="71">
         <f>_xlfn.FORECAST.LINEAR(H$54, CHOOSE({1,2},$B58,$G58),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>4531.7699999997858</v>
       </c>
-      <c r="I58" s="72">
+      <c r="I58" s="71">
         <f t="shared" ref="I58:O58" si="3">I57*($B$58+(I54-$B$54)/($G$54-$B$54)*($G$58-$B$58))/(($B$58+(I54-$B$54)/($G$54-$B$54)*($G$58-$B$58))+($B$59+(I54-$B$54)/($G$54-$B$54)*($G$59-$B$59)))</f>
         <v>5059.2075888711406</v>
       </c>
-      <c r="J58" s="72">
+      <c r="J58" s="71">
         <f t="shared" si="3"/>
         <v>5451.4815480823208</v>
       </c>
-      <c r="K58" s="72">
+      <c r="K58" s="71">
         <f t="shared" si="3"/>
         <v>5850.0577647481523</v>
       </c>
-      <c r="L58" s="72">
+      <c r="L58" s="71">
         <f t="shared" si="3"/>
         <v>6338.2354727614102</v>
       </c>
-      <c r="M58" s="72">
+      <c r="M58" s="71">
         <f t="shared" si="3"/>
         <v>6743.9227382104091</v>
       </c>
-      <c r="N58" s="72">
+      <c r="N58" s="71">
         <f t="shared" si="3"/>
         <v>7153.7233996826026</v>
       </c>
-      <c r="O58" s="72">
+      <c r="O58" s="71">
         <f t="shared" si="3"/>
         <v>7565.5620258024846</v>
       </c>
@@ -6446,211 +6754,211 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B59" s="79">
-        <f>'재생에너지설비현황_19~25'!I57</f>
+        <v>190</v>
+      </c>
+      <c r="B59" s="78">
+        <f>'재생에너지설비현황_19~25'!I63</f>
         <v>299.63</v>
       </c>
-      <c r="C59" s="72">
+      <c r="C59" s="71">
         <f>_xlfn.FORECAST.LINEAR(C$54, CHOOSE({1,2},$B59,$G59),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>3099.7040000008419</v>
       </c>
-      <c r="D59" s="72">
+      <c r="D59" s="71">
         <f>_xlfn.FORECAST.LINEAR(D$54, CHOOSE({1,2},$B59,$G59),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>5899.7780000008643</v>
       </c>
-      <c r="E59" s="72">
+      <c r="E59" s="71">
         <f>_xlfn.FORECAST.LINEAR(E$54, CHOOSE({1,2},$B59,$G59),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>8699.8519999999553</v>
       </c>
-      <c r="F59" s="72">
+      <c r="F59" s="71">
         <f>_xlfn.FORECAST.LINEAR(F$54, CHOOSE({1,2},$B59,$G59),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>11499.925999999978</v>
       </c>
-      <c r="G59" s="80">
+      <c r="G59" s="79">
         <f>14.3*1000</f>
         <v>14300</v>
       </c>
-      <c r="H59" s="72">
+      <c r="H59" s="71">
         <f>_xlfn.FORECAST.LINEAR(H$54, CHOOSE({1,2},$B59,$G59),CHOOSE({1,2},$B$54,$G$54))</f>
         <v>17100.074000000022</v>
       </c>
-      <c r="I59" s="72">
+      <c r="I59" s="71">
         <f t="shared" ref="I59:O59" si="4">I57-I58</f>
         <v>19808.792411128859</v>
       </c>
-      <c r="J59" s="72">
+      <c r="J59" s="71">
         <f t="shared" si="4"/>
         <v>21967.51845191768</v>
       </c>
-      <c r="K59" s="72">
+      <c r="K59" s="71">
         <f t="shared" si="4"/>
         <v>24122.942235251849</v>
       </c>
-      <c r="L59" s="72">
+      <c r="L59" s="71">
         <f t="shared" si="4"/>
         <v>26633.764527238589</v>
       </c>
-      <c r="M59" s="72">
+      <c r="M59" s="71">
         <f t="shared" si="4"/>
         <v>28788.077261789593</v>
       </c>
-      <c r="N59" s="72">
+      <c r="N59" s="71">
         <f t="shared" si="4"/>
         <v>30947.276600317397</v>
       </c>
-      <c r="O59" s="72">
+      <c r="O59" s="71">
         <f t="shared" si="4"/>
         <v>33105.437974197514</v>
       </c>
       <c r="P59" s="34"/>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" s="89" t="s">
-        <v>202</v>
-      </c>
-      <c r="B60" s="89">
+      <c r="A60" s="88" t="s">
+        <v>201</v>
+      </c>
+      <c r="B60" s="88">
         <f>SUM(B58:B59)</f>
         <v>1526.7799999999997</v>
       </c>
-      <c r="C60" s="89">
+      <c r="C60" s="88">
         <f t="shared" ref="C60:O60" si="5">SUM(C58:C59)</f>
         <v>4877.6240000007674</v>
       </c>
-      <c r="D60" s="89">
+      <c r="D60" s="88">
         <f t="shared" si="5"/>
         <v>8228.4680000008084</v>
       </c>
-      <c r="E60" s="89">
+      <c r="E60" s="88">
         <f t="shared" si="5"/>
         <v>11579.311999999918</v>
       </c>
-      <c r="F60" s="89">
+      <c r="F60" s="88">
         <f t="shared" si="5"/>
         <v>14930.155999999959</v>
       </c>
-      <c r="G60" s="89">
+      <c r="G60" s="88">
         <f t="shared" si="5"/>
         <v>18281</v>
       </c>
-      <c r="H60" s="89">
+      <c r="H60" s="88">
         <f t="shared" si="5"/>
         <v>21631.843999999808</v>
       </c>
-      <c r="I60" s="89">
+      <c r="I60" s="88">
         <f t="shared" si="5"/>
         <v>24868</v>
       </c>
-      <c r="J60" s="89">
+      <c r="J60" s="88">
         <f t="shared" si="5"/>
         <v>27419</v>
       </c>
-      <c r="K60" s="89">
+      <c r="K60" s="88">
         <f t="shared" si="5"/>
         <v>29973</v>
       </c>
-      <c r="L60" s="89">
+      <c r="L60" s="88">
         <f t="shared" si="5"/>
         <v>32972</v>
       </c>
-      <c r="M60" s="89">
+      <c r="M60" s="88">
         <f t="shared" si="5"/>
         <v>35532</v>
       </c>
-      <c r="N60" s="89">
+      <c r="N60" s="88">
         <f t="shared" si="5"/>
         <v>38101</v>
       </c>
-      <c r="O60" s="89">
+      <c r="O60" s="88">
         <f t="shared" si="5"/>
         <v>40671</v>
       </c>
       <c r="P60" s="34"/>
     </row>
     <row r="61" spans="1:16">
-      <c r="A61" s="89" t="s">
-        <v>203</v>
-      </c>
-      <c r="B61" s="90">
+      <c r="A61" s="88" t="s">
+        <v>202</v>
+      </c>
+      <c r="B61" s="89">
         <f>B60-B57</f>
         <v>-1490.2200000000003</v>
       </c>
-      <c r="C61" s="90">
+      <c r="C61" s="89">
         <f t="shared" ref="C61:O61" si="6">C60-C57</f>
         <v>919.62400000076741</v>
       </c>
-      <c r="D61" s="90">
+      <c r="D61" s="89">
         <f t="shared" si="6"/>
         <v>2245.4680000008084</v>
       </c>
-      <c r="E61" s="90">
+      <c r="E61" s="89">
         <f t="shared" si="6"/>
         <v>2860.311999999918</v>
       </c>
-      <c r="F61" s="90">
+      <c r="F61" s="89">
         <f t="shared" si="6"/>
         <v>269.15599999995902</v>
       </c>
-      <c r="G61" s="90">
+      <c r="G61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H61" s="90">
+      <c r="H61" s="89">
         <f t="shared" si="6"/>
         <v>-689.15600000019185</v>
       </c>
-      <c r="I61" s="90">
+      <c r="I61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J61" s="90">
+      <c r="J61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K61" s="90">
+      <c r="K61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L61" s="90">
+      <c r="L61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M61" s="90">
+      <c r="M61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N61" s="90">
+      <c r="N61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O61" s="90">
+      <c r="O61" s="89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P61" s="34"/>
     </row>
-    <row r="63" spans="1:16" ht="15.75">
-      <c r="A63" s="81" t="s">
-        <v>205</v>
-      </c>
-      <c r="B63" s="81"/>
-      <c r="C63" s="81"/>
-      <c r="D63" s="81"/>
-      <c r="E63" s="81"/>
-      <c r="F63" s="81"/>
-      <c r="G63" s="81"/>
-      <c r="H63" s="81"/>
-      <c r="I63" s="81"/>
-      <c r="J63" s="81"/>
-      <c r="K63" s="81"/>
-      <c r="L63" s="81"/>
-      <c r="M63" s="81"/>
-      <c r="N63" s="81"/>
-      <c r="O63" s="81"/>
-    </row>
-    <row r="64" spans="1:16" ht="15.75" thickBot="1"/>
-    <row r="65" spans="1:15" ht="15.75" thickBot="1">
+    <row r="63" spans="1:16" ht="15.5">
+      <c r="A63" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="B63" s="80"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="80"/>
+      <c r="E63" s="80"/>
+      <c r="F63" s="80"/>
+      <c r="G63" s="80"/>
+      <c r="H63" s="80"/>
+      <c r="I63" s="80"/>
+      <c r="J63" s="80"/>
+      <c r="K63" s="80"/>
+      <c r="L63" s="80"/>
+      <c r="M63" s="80"/>
+      <c r="N63" s="80"/>
+      <c r="O63" s="80"/>
+    </row>
+    <row r="64" spans="1:16" ht="15" thickBot="1"/>
+    <row r="65" spans="1:15" ht="15" thickBot="1">
       <c r="A65" s="46" t="s">
         <v>80</v>
       </c>
@@ -6821,7 +7129,7 @@
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B68" s="35">
         <f>'설비현황_19~25'!H30</f>
@@ -6882,7 +7190,7 @@
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B69" s="36">
         <f>'설비현황_19~25'!H38</f>
@@ -7290,8 +7598,8 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15.75" thickBot="1"/>
-    <row r="84" spans="1:15" ht="15.75" thickBot="1">
+    <row r="83" spans="1:15" ht="15" thickBot="1"/>
+    <row r="84" spans="1:15" ht="15" thickBot="1">
       <c r="A84" s="46" t="s">
         <v>80</v>
       </c>
@@ -7546,18 +7854,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0FC3DE-FB57-4949-8ACD-A608751B1C98}">
   <dimension ref="A2:AN48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="17" max="17" width="10.28515625" customWidth="1"/>
-    <col min="19" max="19" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" customWidth="1"/>
-    <col min="21" max="21" width="6.5703125" customWidth="1"/>
+    <col min="1" max="1" width="31.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" customWidth="1"/>
+    <col min="17" max="17" width="10.26953125" customWidth="1"/>
+    <col min="19" max="19" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.08984375" customWidth="1"/>
+    <col min="21" max="21" width="6.6328125" customWidth="1"/>
     <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:26">
@@ -7948,7 +8256,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" thickBot="1">
+    <row r="14" spans="1:26" ht="15" thickBot="1">
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="9"/>
@@ -7959,7 +8267,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" thickBot="1">
+    <row r="15" spans="1:26" ht="15" thickBot="1">
       <c r="A15" s="46" t="s">
         <v>80</v>
       </c>
@@ -8387,7 +8695,7 @@
       </c>
       <c r="AN20" s="9"/>
     </row>
-    <row r="21" spans="1:40" ht="15.75" thickBot="1">
+    <row r="21" spans="1:40" ht="15" thickBot="1">
       <c r="A21" s="56" t="s">
         <v>121</v>
       </c>
@@ -8537,7 +8845,7 @@
       <c r="A25" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="76">
+      <c r="B25" s="75">
         <f>'설비현황_19~25'!H25</f>
         <v>1050</v>
       </c>
@@ -8586,7 +8894,7 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="76">
+      <c r="B26" s="75">
         <f>'설비현황_19~25'!H26</f>
         <v>0</v>
       </c>
@@ -8634,7 +8942,7 @@
       <c r="A27" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="76">
+      <c r="B27" s="75">
         <f>'설비현황_19~25'!H27</f>
         <v>1332.4</v>
       </c>
@@ -8695,7 +9003,7 @@
       <c r="A28" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="76">
+      <c r="B28" s="75">
         <f>'설비현황_19~25'!H28</f>
         <v>0</v>
       </c>
@@ -8756,7 +9064,7 @@
       <c r="A29" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="76">
+      <c r="B29" s="75">
         <f>'설비현황_19~25'!H29</f>
         <v>0</v>
       </c>
@@ -8804,59 +9112,59 @@
       <c r="A30" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="76">
+      <c r="B30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!B68</f>
         <v>620.69999999999982</v>
       </c>
-      <c r="C30" s="76">
+      <c r="C30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!C68</f>
         <v>154.6698592950944</v>
       </c>
-      <c r="D30" s="76">
+      <c r="D30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!D68</f>
         <v>332.84427744175019</v>
       </c>
-      <c r="E30" s="76">
+      <c r="E30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!E68</f>
         <v>449.70960152142305</v>
       </c>
-      <c r="F30" s="76">
+      <c r="F30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!F68</f>
         <v>976.67194891796532</v>
       </c>
-      <c r="G30" s="76">
+      <c r="G30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!G68</f>
         <v>595.01051078475837</v>
       </c>
-      <c r="H30" s="76">
+      <c r="H30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!H68</f>
         <v>664.04487943910908</v>
       </c>
-      <c r="I30" s="76">
+      <c r="I30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!I68</f>
         <v>415.11705209985587</v>
       </c>
-      <c r="J30" s="76">
+      <c r="J30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!J68</f>
         <v>392.27395921118011</v>
       </c>
-      <c r="K30" s="76">
+      <c r="K30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!K68</f>
         <v>398.57621666583145</v>
       </c>
-      <c r="L30" s="76">
+      <c r="L30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!L68</f>
         <v>488.17770801325815</v>
       </c>
-      <c r="M30" s="76">
+      <c r="M30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!M68</f>
         <v>405.68726544899846</v>
       </c>
-      <c r="N30" s="76">
+      <c r="N30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!N68</f>
         <v>409.80066147219389</v>
       </c>
-      <c r="O30" s="76">
+      <c r="O30" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!O68</f>
         <v>411.83862611988224</v>
       </c>
@@ -8865,59 +9173,59 @@
       <c r="A31" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="76">
+      <c r="B31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!B67</f>
         <v>3814</v>
       </c>
-      <c r="C31" s="76">
+      <c r="C31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!C67</f>
         <v>4126</v>
       </c>
-      <c r="D31" s="76">
+      <c r="D31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!D67</f>
         <v>4327</v>
       </c>
-      <c r="E31" s="76">
+      <c r="E31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!E67</f>
         <v>4405</v>
       </c>
-      <c r="F31" s="76">
+      <c r="F31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!F67</f>
         <v>4450</v>
       </c>
-      <c r="G31" s="76">
+      <c r="G31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!G67</f>
         <v>6403</v>
       </c>
-      <c r="H31" s="76">
+      <c r="H31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!H67</f>
         <v>3036</v>
       </c>
-      <c r="I31" s="76">
+      <c r="I31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!I67</f>
         <v>3028</v>
       </c>
-      <c r="J31" s="76">
+      <c r="J31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!J67</f>
         <v>3024</v>
       </c>
-      <c r="K31" s="76">
+      <c r="K31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!K67</f>
         <v>3021</v>
       </c>
-      <c r="L31" s="76">
+      <c r="L31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!L67</f>
         <v>3027</v>
       </c>
-      <c r="M31" s="76">
+      <c r="M31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!M67</f>
         <v>2130</v>
       </c>
-      <c r="N31" s="76">
+      <c r="N31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!N67</f>
         <v>2131</v>
       </c>
-      <c r="O31" s="76">
+      <c r="O31" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!O67</f>
         <v>2131</v>
       </c>
@@ -8926,7 +9234,7 @@
       <c r="A32" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="76">
+      <c r="B32" s="75">
         <f>'설비현황_19~25'!H32</f>
         <v>0</v>
       </c>
@@ -8974,7 +9282,7 @@
       <c r="A33" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="76">
+      <c r="B33" s="75">
         <f>'설비현황_19~25'!H33</f>
         <v>0</v>
       </c>
@@ -9022,7 +9330,7 @@
       <c r="A34" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="76">
+      <c r="B34" s="75">
         <f>'설비현황_19~25'!H34</f>
         <v>0</v>
       </c>
@@ -9070,7 +9378,7 @@
       <c r="A35" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="76">
+      <c r="B35" s="75">
         <f>'설비현황_19~25'!H35</f>
         <v>0</v>
       </c>
@@ -9118,7 +9426,7 @@
       <c r="A36" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="76">
+      <c r="B36" s="75">
         <f>'설비현황_19~25'!H36</f>
         <v>0</v>
       </c>
@@ -9166,7 +9474,7 @@
       <c r="A37" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="76">
+      <c r="B37" s="75">
         <f>'설비현황_19~25'!H37</f>
         <v>0</v>
       </c>
@@ -9214,59 +9522,59 @@
       <c r="A38" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="76">
+      <c r="B38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!B69</f>
         <v>103.30000000000001</v>
       </c>
-      <c r="C38" s="76">
+      <c r="C38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!C69</f>
         <v>786.3301407049056</v>
       </c>
-      <c r="D38" s="76">
+      <c r="D38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!D69</f>
         <v>1692.1557225582499</v>
       </c>
-      <c r="E38" s="76">
+      <c r="E38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!E69</f>
         <v>2286.2903984785771</v>
       </c>
-      <c r="F38" s="76">
+      <c r="F38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!F69</f>
         <v>4965.328051082035</v>
       </c>
-      <c r="G38" s="76">
+      <c r="G38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!G69</f>
         <v>3024.9894892152415</v>
       </c>
-      <c r="H38" s="76">
+      <c r="H38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!H69</f>
         <v>3375.9551205608909</v>
       </c>
-      <c r="I38" s="76">
+      <c r="I38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!I69</f>
         <v>2131.8829479001442</v>
       </c>
-      <c r="J38" s="76">
+      <c r="J38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!J69</f>
         <v>2158.7260407888198</v>
       </c>
-      <c r="K38" s="76">
+      <c r="K38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!K69</f>
         <v>2155.4237833341685</v>
       </c>
-      <c r="L38" s="76">
+      <c r="L38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!L69</f>
         <v>2510.8222919867421</v>
       </c>
-      <c r="M38" s="76">
+      <c r="M38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!M69</f>
         <v>2154.3127345510015</v>
       </c>
-      <c r="N38" s="76">
+      <c r="N38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!N69</f>
         <v>2159.199338527806</v>
       </c>
-      <c r="O38" s="76">
+      <c r="O38" s="75">
         <f>'신재생에너지 설비 및 발전량 전망_24~38'!O69</f>
         <v>2158.1613738801179</v>
       </c>
@@ -9275,7 +9583,7 @@
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="76">
+      <c r="B39" s="75">
         <f>'설비현황_19~25'!H39</f>
         <v>0</v>
       </c>
@@ -9323,7 +9631,7 @@
       <c r="A40" t="s">
         <v>23</v>
       </c>
-      <c r="B40" s="76">
+      <c r="B40" s="75">
         <f>'설비현황_19~25'!H40</f>
         <v>0</v>
       </c>
@@ -9371,7 +9679,7 @@
       <c r="A41" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="76">
+      <c r="B41" s="75">
         <f>'설비현황_19~25'!H41</f>
         <v>0</v>
       </c>
@@ -9419,7 +9727,7 @@
       <c r="A42" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="76">
+      <c r="B42" s="75">
         <f>'설비현황_19~25'!H42</f>
         <v>0</v>
       </c>
@@ -9480,7 +9788,7 @@
       <c r="A43" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="76">
+      <c r="B43" s="75">
         <f>'설비현황_19~25'!H43</f>
         <v>0</v>
       </c>
@@ -9528,7 +9836,7 @@
       <c r="A44" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="76">
+      <c r="B44" s="75">
         <f>'설비현황_19~25'!H44</f>
         <v>0</v>
       </c>
@@ -9576,7 +9884,7 @@
       <c r="A45" t="s">
         <v>28</v>
       </c>
-      <c r="B45" s="76">
+      <c r="B45" s="75">
         <f>'설비현황_19~25'!H45</f>
         <v>0</v>
       </c>
@@ -9624,7 +9932,7 @@
       <c r="A46" t="s">
         <v>8</v>
       </c>
-      <c r="B46" s="76">
+      <c r="B46" s="75">
         <f>'설비현황_19~25'!H46</f>
         <v>0</v>
       </c>
@@ -9685,7 +9993,7 @@
       <c r="A47" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="76">
+      <c r="B47" s="75">
         <f>'설비현황_19~25'!H47</f>
         <v>0</v>
       </c>
@@ -9733,7 +10041,7 @@
       <c r="A48" t="s">
         <v>79</v>
       </c>
-      <c r="B48" s="76">
+      <c r="B48" s="75">
         <f>'설비현황_19~25'!H48</f>
         <v>0</v>
       </c>
@@ -9802,12 +10110,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" customWidth="1"/>
+    <col min="3" max="3" width="8.26953125" customWidth="1"/>
+    <col min="10" max="10" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -9915,131 +10223,131 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="76">
+      <c r="B2" s="75">
         <f>'설비현황_19~25'!B25</f>
         <v>0</v>
       </c>
-      <c r="C2" s="76">
+      <c r="C2" s="75">
         <f>'설비현황_19~25'!C25</f>
         <v>0</v>
       </c>
-      <c r="D2" s="76">
+      <c r="D2" s="75">
         <f>'설비현황_19~25'!D25</f>
         <v>3098</v>
       </c>
-      <c r="E2" s="76">
+      <c r="E2" s="75">
         <f>'설비현황_19~25'!E25</f>
         <v>2080</v>
       </c>
-      <c r="F2" s="76">
+      <c r="F2" s="75">
         <f>'설비현황_19~25'!F25</f>
         <v>0</v>
       </c>
-      <c r="G2" s="76">
+      <c r="G2" s="75">
         <f>'설비현황_19~25'!G25</f>
         <v>1050</v>
       </c>
-      <c r="H2" s="76">
+      <c r="H2" s="75">
         <f>'설비현황_19~25'!H25</f>
         <v>1050</v>
       </c>
-      <c r="I2" s="76">
+      <c r="I2" s="75">
         <f>'건설계획표_26~38'!C25</f>
         <v>0</v>
       </c>
-      <c r="J2" s="76">
+      <c r="J2" s="75">
         <f>'건설계획표_26~38'!D25</f>
         <v>0</v>
       </c>
-      <c r="K2" s="76">
+      <c r="K2" s="75">
         <f>'건설계획표_26~38'!E25</f>
         <v>0</v>
       </c>
-      <c r="L2" s="76">
+      <c r="L2" s="75">
         <f>'건설계획표_26~38'!F25</f>
         <v>0</v>
       </c>
-      <c r="M2" s="76">
+      <c r="M2" s="75">
         <f>'건설계획표_26~38'!G25</f>
         <v>0</v>
       </c>
-      <c r="N2" s="76">
+      <c r="N2" s="75">
         <f>'건설계획표_26~38'!H25</f>
         <v>0</v>
       </c>
-      <c r="O2" s="76">
+      <c r="O2" s="75">
         <f>'건설계획표_26~38'!I25</f>
         <v>0</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="75">
         <f>'건설계획표_26~38'!J25</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="76">
+      <c r="Q2" s="75">
         <f>'건설계획표_26~38'!K25</f>
         <v>0</v>
       </c>
-      <c r="R2" s="76">
+      <c r="R2" s="75">
         <f>'건설계획표_26~38'!L25</f>
         <v>0</v>
       </c>
-      <c r="S2" s="76">
+      <c r="S2" s="75">
         <f>'건설계획표_26~38'!M25</f>
         <v>0</v>
       </c>
-      <c r="T2" s="76">
+      <c r="T2" s="75">
         <f>'건설계획표_26~38'!N25</f>
         <v>0</v>
       </c>
-      <c r="U2" s="76">
+      <c r="U2" s="75">
         <f>'건설계획표_26~38'!O25</f>
         <v>0</v>
       </c>
-      <c r="V2" s="76">
+      <c r="V2" s="75">
         <f>'건설계획표_26~38'!P25</f>
         <v>0</v>
       </c>
-      <c r="W2" s="76">
+      <c r="W2" s="75">
         <f>'건설계획표_26~38'!Q25</f>
         <v>0</v>
       </c>
-      <c r="X2" s="76">
+      <c r="X2" s="75">
         <f>'건설계획표_26~38'!R25</f>
         <v>0</v>
       </c>
-      <c r="Y2" s="76">
+      <c r="Y2" s="75">
         <f>'건설계획표_26~38'!S25</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="76">
+      <c r="Z2" s="75">
         <f>'건설계획표_26~38'!T25</f>
         <v>0</v>
       </c>
-      <c r="AA2" s="76">
+      <c r="AA2" s="75">
         <f>'건설계획표_26~38'!U25</f>
         <v>0</v>
       </c>
-      <c r="AB2" s="76">
+      <c r="AB2" s="75">
         <f>'건설계획표_26~38'!V25</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="76">
+      <c r="AC2" s="75">
         <f>'건설계획표_26~38'!W25</f>
         <v>0</v>
       </c>
-      <c r="AD2" s="76">
+      <c r="AD2" s="75">
         <f>'건설계획표_26~38'!X25</f>
         <v>0</v>
       </c>
-      <c r="AE2" s="76">
+      <c r="AE2" s="75">
         <f>'건설계획표_26~38'!Y25</f>
         <v>0</v>
       </c>
-      <c r="AF2" s="76">
+      <c r="AF2" s="75">
         <f>'건설계획표_26~38'!Z25</f>
         <v>0</v>
       </c>
-      <c r="AG2" s="76">
+      <c r="AG2" s="75">
         <f>'건설계획표_26~38'!AA25</f>
         <v>0</v>
       </c>
@@ -10048,131 +10356,131 @@
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="76">
+      <c r="B3" s="75">
         <f>'설비현황_19~25'!B26</f>
         <v>0</v>
       </c>
-      <c r="C3" s="76">
+      <c r="C3" s="75">
         <f>'설비현황_19~25'!C26</f>
         <v>0</v>
       </c>
-      <c r="D3" s="76">
+      <c r="D3" s="75">
         <f>'설비현황_19~25'!D26</f>
         <v>0</v>
       </c>
-      <c r="E3" s="76">
+      <c r="E3" s="75">
         <f>'설비현황_19~25'!E26</f>
         <v>0</v>
       </c>
-      <c r="F3" s="76">
+      <c r="F3" s="75">
         <f>'설비현황_19~25'!F26</f>
         <v>0</v>
       </c>
-      <c r="G3" s="76">
+      <c r="G3" s="75">
         <f>'설비현황_19~25'!G26</f>
         <v>0</v>
       </c>
-      <c r="H3" s="76">
+      <c r="H3" s="75">
         <f>'설비현황_19~25'!H26</f>
         <v>0</v>
       </c>
-      <c r="I3" s="76">
+      <c r="I3" s="75">
         <f>'건설계획표_26~38'!C26</f>
         <v>0</v>
       </c>
-      <c r="J3" s="76">
+      <c r="J3" s="75">
         <f>'건설계획표_26~38'!D26</f>
         <v>0</v>
       </c>
-      <c r="K3" s="76">
+      <c r="K3" s="75">
         <f>'건설계획표_26~38'!E26</f>
         <v>0</v>
       </c>
-      <c r="L3" s="76">
+      <c r="L3" s="75">
         <f>'건설계획표_26~38'!F26</f>
         <v>0</v>
       </c>
-      <c r="M3" s="76">
+      <c r="M3" s="75">
         <f>'건설계획표_26~38'!G26</f>
         <v>0</v>
       </c>
-      <c r="N3" s="76">
+      <c r="N3" s="75">
         <f>'건설계획표_26~38'!H26</f>
         <v>0</v>
       </c>
-      <c r="O3" s="76">
+      <c r="O3" s="75">
         <f>'건설계획표_26~38'!I26</f>
         <v>0</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="75">
         <f>'건설계획표_26~38'!J26</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="76">
+      <c r="Q3" s="75">
         <f>'건설계획표_26~38'!K26</f>
         <v>0</v>
       </c>
-      <c r="R3" s="76">
+      <c r="R3" s="75">
         <f>'건설계획표_26~38'!L26</f>
         <v>0</v>
       </c>
-      <c r="S3" s="76">
+      <c r="S3" s="75">
         <f>'건설계획표_26~38'!M26</f>
         <v>0</v>
       </c>
-      <c r="T3" s="76">
+      <c r="T3" s="75">
         <f>'건설계획표_26~38'!N26</f>
         <v>0</v>
       </c>
-      <c r="U3" s="76">
+      <c r="U3" s="75">
         <f>'건설계획표_26~38'!O26</f>
         <v>0</v>
       </c>
-      <c r="V3" s="76">
+      <c r="V3" s="75">
         <f>'건설계획표_26~38'!P26</f>
         <v>0</v>
       </c>
-      <c r="W3" s="76">
+      <c r="W3" s="75">
         <f>'건설계획표_26~38'!Q26</f>
         <v>0</v>
       </c>
-      <c r="X3" s="76">
+      <c r="X3" s="75">
         <f>'건설계획표_26~38'!R26</f>
         <v>0</v>
       </c>
-      <c r="Y3" s="76">
+      <c r="Y3" s="75">
         <f>'건설계획표_26~38'!S26</f>
         <v>0</v>
       </c>
-      <c r="Z3" s="76">
+      <c r="Z3" s="75">
         <f>'건설계획표_26~38'!T26</f>
         <v>0</v>
       </c>
-      <c r="AA3" s="76">
+      <c r="AA3" s="75">
         <f>'건설계획표_26~38'!U26</f>
         <v>0</v>
       </c>
-      <c r="AB3" s="76">
+      <c r="AB3" s="75">
         <f>'건설계획표_26~38'!V26</f>
         <v>0</v>
       </c>
-      <c r="AC3" s="76">
+      <c r="AC3" s="75">
         <f>'건설계획표_26~38'!W26</f>
         <v>0</v>
       </c>
-      <c r="AD3" s="76">
+      <c r="AD3" s="75">
         <f>'건설계획표_26~38'!X26</f>
         <v>0</v>
       </c>
-      <c r="AE3" s="76">
+      <c r="AE3" s="75">
         <f>'건설계획표_26~38'!Y26</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="76">
+      <c r="AF3" s="75">
         <f>'건설계획표_26~38'!Z26</f>
         <v>0</v>
       </c>
-      <c r="AG3" s="76">
+      <c r="AG3" s="75">
         <f>'건설계획표_26~38'!AA26</f>
         <v>0</v>
       </c>
@@ -10181,131 +10489,131 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="76">
+      <c r="B4" s="75">
         <f>'설비현황_19~25'!B27</f>
         <v>1601.646</v>
       </c>
-      <c r="C4" s="76">
+      <c r="C4" s="75">
         <f>'설비현황_19~25'!C27</f>
         <v>158.79599999999999</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="75">
         <f>'설비현황_19~25'!D27</f>
         <v>481.69</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="75">
         <f>'설비현황_19~25'!E27</f>
         <v>0</v>
       </c>
-      <c r="F4" s="76">
+      <c r="F4" s="75">
         <f>'설비현황_19~25'!F27</f>
         <v>1989.8320000000001</v>
       </c>
-      <c r="G4" s="76">
+      <c r="G4" s="75">
         <f>'설비현황_19~25'!G27</f>
         <v>2983.7709999999997</v>
       </c>
-      <c r="H4" s="76">
+      <c r="H4" s="75">
         <f>'설비현황_19~25'!H27</f>
         <v>1332.4</v>
       </c>
-      <c r="I4" s="76">
+      <c r="I4" s="75">
         <f>'건설계획표_26~38'!C27</f>
         <v>3548</v>
       </c>
-      <c r="J4" s="76">
+      <c r="J4" s="75">
         <f>'건설계획표_26~38'!D27</f>
         <v>3420</v>
       </c>
-      <c r="K4" s="76">
+      <c r="K4" s="75">
         <f>'건설계획표_26~38'!E27</f>
         <v>2700</v>
       </c>
-      <c r="L4" s="76">
+      <c r="L4" s="75">
         <f>'건설계획표_26~38'!F27</f>
         <v>2409</v>
       </c>
-      <c r="M4" s="76">
+      <c r="M4" s="75">
         <f>'건설계획표_26~38'!G27</f>
         <v>1000</v>
       </c>
-      <c r="N4" s="76">
+      <c r="N4" s="75">
         <f>'건설계획표_26~38'!H27</f>
         <v>1285</v>
       </c>
-      <c r="O4" s="76">
+      <c r="O4" s="75">
         <f>'건설계획표_26~38'!I27</f>
         <v>2489.39</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="75">
         <f>'건설계획표_26~38'!J27</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="76">
+      <c r="Q4" s="75">
         <f>'건설계획표_26~38'!K27</f>
         <v>1600</v>
       </c>
-      <c r="R4" s="76">
+      <c r="R4" s="75">
         <f>'건설계획표_26~38'!L27</f>
         <v>0</v>
       </c>
-      <c r="S4" s="76">
+      <c r="S4" s="75">
         <f>'건설계획표_26~38'!M27</f>
         <v>1000</v>
       </c>
-      <c r="T4" s="76">
+      <c r="T4" s="75">
         <f>'건설계획표_26~38'!N27</f>
         <v>0</v>
       </c>
-      <c r="U4" s="76">
+      <c r="U4" s="75">
         <f>'건설계획표_26~38'!O27</f>
         <v>0</v>
       </c>
-      <c r="V4" s="76">
+      <c r="V4" s="75">
         <f>'건설계획표_26~38'!P27</f>
         <v>0</v>
       </c>
-      <c r="W4" s="76">
+      <c r="W4" s="75">
         <f>'건설계획표_26~38'!Q27</f>
         <v>0</v>
       </c>
-      <c r="X4" s="76">
+      <c r="X4" s="75">
         <f>'건설계획표_26~38'!R27</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="76">
+      <c r="Y4" s="75">
         <f>'건설계획표_26~38'!S27</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="76">
+      <c r="Z4" s="75">
         <f>'건설계획표_26~38'!T27</f>
         <v>0</v>
       </c>
-      <c r="AA4" s="76">
+      <c r="AA4" s="75">
         <f>'건설계획표_26~38'!U27</f>
         <v>0</v>
       </c>
-      <c r="AB4" s="76">
+      <c r="AB4" s="75">
         <f>'건설계획표_26~38'!V27</f>
         <v>0</v>
       </c>
-      <c r="AC4" s="76">
+      <c r="AC4" s="75">
         <f>'건설계획표_26~38'!W27</f>
         <v>0</v>
       </c>
-      <c r="AD4" s="76">
+      <c r="AD4" s="75">
         <f>'건설계획표_26~38'!X27</f>
         <v>0</v>
       </c>
-      <c r="AE4" s="76">
+      <c r="AE4" s="75">
         <f>'건설계획표_26~38'!Y27</f>
         <v>0</v>
       </c>
-      <c r="AF4" s="76">
+      <c r="AF4" s="75">
         <f>'건설계획표_26~38'!Z27</f>
         <v>0</v>
       </c>
-      <c r="AG4" s="76">
+      <c r="AG4" s="75">
         <f>'건설계획표_26~38'!AA27</f>
         <v>0</v>
       </c>
@@ -10314,130 +10622,130 @@
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="76">
-        <v>0</v>
-      </c>
-      <c r="C5" s="76">
+      <c r="B5" s="75">
+        <v>0</v>
+      </c>
+      <c r="C5" s="75">
         <f>'설비현황_19~25'!C28</f>
         <v>0</v>
       </c>
-      <c r="D5" s="76">
+      <c r="D5" s="75">
         <f>'설비현황_19~25'!D28</f>
         <v>0</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="75">
         <f>'설비현황_19~25'!E28</f>
         <v>1400</v>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="75">
         <f>'설비현황_19~25'!F28</f>
         <v>0</v>
       </c>
-      <c r="G5" s="76">
+      <c r="G5" s="75">
         <f>'설비현황_19~25'!G28</f>
         <v>1400</v>
       </c>
-      <c r="H5" s="76">
+      <c r="H5" s="75">
         <f>'설비현황_19~25'!H28</f>
         <v>0</v>
       </c>
-      <c r="I5" s="76">
+      <c r="I5" s="75">
         <f>'건설계획표_26~38'!C28</f>
         <v>2800</v>
       </c>
-      <c r="J5" s="76">
+      <c r="J5" s="75">
         <f>'건설계획표_26~38'!D28</f>
         <v>0</v>
       </c>
-      <c r="K5" s="76">
+      <c r="K5" s="75">
         <f>'건설계획표_26~38'!E28</f>
         <v>0</v>
       </c>
-      <c r="L5" s="76">
+      <c r="L5" s="75">
         <f>'건설계획표_26~38'!F28</f>
         <v>0</v>
       </c>
-      <c r="M5" s="76">
+      <c r="M5" s="75">
         <f>'건설계획표_26~38'!G28</f>
         <v>0</v>
       </c>
-      <c r="N5" s="76">
+      <c r="N5" s="75">
         <f>'건설계획표_26~38'!H28</f>
         <v>0</v>
       </c>
-      <c r="O5" s="76">
+      <c r="O5" s="75">
         <f>'건설계획표_26~38'!I28</f>
         <v>1400</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="75">
         <f>'건설계획표_26~38'!J28</f>
         <v>1400</v>
       </c>
-      <c r="Q5" s="76">
+      <c r="Q5" s="75">
         <f>'건설계획표_26~38'!K28</f>
         <v>0</v>
       </c>
-      <c r="R5" s="76">
+      <c r="R5" s="75">
         <f>'건설계획표_26~38'!L28</f>
         <v>0</v>
       </c>
-      <c r="S5" s="76">
+      <c r="S5" s="75">
         <f>'건설계획표_26~38'!M28</f>
         <v>0</v>
       </c>
-      <c r="T5" s="76">
+      <c r="T5" s="75">
         <f>'건설계획표_26~38'!N28</f>
         <v>1400</v>
       </c>
-      <c r="U5" s="76">
+      <c r="U5" s="75">
         <f>'건설계획표_26~38'!O28</f>
         <v>1400</v>
       </c>
-      <c r="V5" s="76">
+      <c r="V5" s="75">
         <f>'건설계획표_26~38'!P28</f>
         <v>0</v>
       </c>
-      <c r="W5" s="76">
+      <c r="W5" s="75">
         <f>'건설계획표_26~38'!Q28</f>
         <v>0</v>
       </c>
-      <c r="X5" s="76">
+      <c r="X5" s="75">
         <f>'건설계획표_26~38'!R28</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="76">
+      <c r="Y5" s="75">
         <f>'건설계획표_26~38'!S28</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="76">
+      <c r="Z5" s="75">
         <f>'건설계획표_26~38'!T28</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="76">
+      <c r="AA5" s="75">
         <f>'건설계획표_26~38'!U28</f>
         <v>0</v>
       </c>
-      <c r="AB5" s="76">
+      <c r="AB5" s="75">
         <f>'건설계획표_26~38'!V28</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="76">
+      <c r="AC5" s="75">
         <f>'건설계획표_26~38'!W28</f>
         <v>0</v>
       </c>
-      <c r="AD5" s="76">
+      <c r="AD5" s="75">
         <f>'건설계획표_26~38'!X28</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="76">
+      <c r="AE5" s="75">
         <f>'건설계획표_26~38'!Y28</f>
         <v>0</v>
       </c>
-      <c r="AF5" s="76">
+      <c r="AF5" s="75">
         <f>'건설계획표_26~38'!Z28</f>
         <v>0</v>
       </c>
-      <c r="AG5" s="76">
+      <c r="AG5" s="75">
         <f>'건설계획표_26~38'!AA28</f>
         <v>0</v>
       </c>
@@ -10446,131 +10754,131 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="75">
         <f>'설비현황_19~25'!B29</f>
         <v>0</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="75">
         <f>'설비현황_19~25'!C29</f>
         <v>0</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="75">
         <f>'설비현황_19~25'!D29</f>
         <v>0</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="75">
         <f>'설비현황_19~25'!E29</f>
         <v>0</v>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="75">
         <f>'설비현황_19~25'!F29</f>
         <v>0</v>
       </c>
-      <c r="G6" s="76">
+      <c r="G6" s="75">
         <f>'설비현황_19~25'!G29</f>
         <v>0</v>
       </c>
-      <c r="H6" s="76">
+      <c r="H6" s="75">
         <f>'설비현황_19~25'!H29</f>
         <v>0</v>
       </c>
-      <c r="I6" s="76">
+      <c r="I6" s="75">
         <f>'건설계획표_26~38'!C29</f>
         <v>0</v>
       </c>
-      <c r="J6" s="76">
+      <c r="J6" s="75">
         <f>'건설계획표_26~38'!D29</f>
         <v>0</v>
       </c>
-      <c r="K6" s="76">
+      <c r="K6" s="75">
         <f>'건설계획표_26~38'!E29</f>
         <v>0</v>
       </c>
-      <c r="L6" s="76">
+      <c r="L6" s="75">
         <f>'건설계획표_26~38'!F29</f>
         <v>0</v>
       </c>
-      <c r="M6" s="76">
+      <c r="M6" s="75">
         <f>'건설계획표_26~38'!G29</f>
         <v>0</v>
       </c>
-      <c r="N6" s="76">
+      <c r="N6" s="75">
         <f>'건설계획표_26~38'!H29</f>
         <v>0</v>
       </c>
-      <c r="O6" s="76">
+      <c r="O6" s="75">
         <f>'건설계획표_26~38'!I29</f>
         <v>0</v>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="75">
         <f>'건설계획표_26~38'!J29</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="76">
+      <c r="Q6" s="75">
         <f>'건설계획표_26~38'!K29</f>
         <v>0</v>
       </c>
-      <c r="R6" s="76">
+      <c r="R6" s="75">
         <f>'건설계획표_26~38'!L29</f>
         <v>0</v>
       </c>
-      <c r="S6" s="76">
+      <c r="S6" s="75">
         <f>'건설계획표_26~38'!M29</f>
         <v>0</v>
       </c>
-      <c r="T6" s="76">
+      <c r="T6" s="75">
         <f>'건설계획표_26~38'!N29</f>
         <v>0</v>
       </c>
-      <c r="U6" s="76">
+      <c r="U6" s="75">
         <f>'건설계획표_26~38'!O29</f>
         <v>0</v>
       </c>
-      <c r="V6" s="76">
+      <c r="V6" s="75">
         <f>'건설계획표_26~38'!P29</f>
         <v>0</v>
       </c>
-      <c r="W6" s="76">
+      <c r="W6" s="75">
         <f>'건설계획표_26~38'!Q29</f>
         <v>0</v>
       </c>
-      <c r="X6" s="76">
+      <c r="X6" s="75">
         <f>'건설계획표_26~38'!R29</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="76">
+      <c r="Y6" s="75">
         <f>'건설계획표_26~38'!S29</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="76">
+      <c r="Z6" s="75">
         <f>'건설계획표_26~38'!T29</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="76">
+      <c r="AA6" s="75">
         <f>'건설계획표_26~38'!U29</f>
         <v>0</v>
       </c>
-      <c r="AB6" s="76">
+      <c r="AB6" s="75">
         <f>'건설계획표_26~38'!V29</f>
         <v>0</v>
       </c>
-      <c r="AC6" s="76">
+      <c r="AC6" s="75">
         <f>'건설계획표_26~38'!W29</f>
         <v>0</v>
       </c>
-      <c r="AD6" s="76">
+      <c r="AD6" s="75">
         <f>'건설계획표_26~38'!X29</f>
         <v>0</v>
       </c>
-      <c r="AE6" s="76">
+      <c r="AE6" s="75">
         <f>'건설계획표_26~38'!Y29</f>
         <v>0</v>
       </c>
-      <c r="AF6" s="76">
+      <c r="AF6" s="75">
         <f>'건설계획표_26~38'!Z29</f>
         <v>0</v>
       </c>
-      <c r="AG6" s="76">
+      <c r="AG6" s="75">
         <f>'건설계획표_26~38'!AA29</f>
         <v>0</v>
       </c>
@@ -10579,131 +10887,131 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="76">
+      <c r="B7" s="75">
         <f>'설비현황_19~25'!B30</f>
         <v>0</v>
       </c>
-      <c r="C7" s="76">
+      <c r="C7" s="75">
         <f>'설비현황_19~25'!C30</f>
         <v>91.399999999999864</v>
       </c>
-      <c r="D7" s="76">
+      <c r="D7" s="75">
         <f>'설비현황_19~25'!D30</f>
         <v>63.600000000000136</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="75">
         <f>'설비현황_19~25'!E30</f>
         <v>98.25</v>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="75">
         <f>'설비현황_19~25'!F30</f>
         <v>0</v>
       </c>
-      <c r="G7" s="76">
+      <c r="G7" s="75">
         <f>'설비현황_19~25'!G30</f>
         <v>353.20000000000005</v>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="75">
         <f>'설비현황_19~25'!H30</f>
         <v>620.69999999999982</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="75">
         <f>'건설계획표_26~38'!C30</f>
         <v>154.6698592950944</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="75">
         <f>'건설계획표_26~38'!D30</f>
         <v>332.84427744175019</v>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="75">
         <f>'건설계획표_26~38'!E30</f>
         <v>449.70960152142305</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="75">
         <f>'건설계획표_26~38'!F30</f>
         <v>976.67194891796532</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="75">
         <f>'건설계획표_26~38'!G30</f>
         <v>595.01051078475837</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="75">
         <f>'건설계획표_26~38'!H30</f>
         <v>664.04487943910908</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="75">
         <f>'건설계획표_26~38'!I30</f>
         <v>415.11705209985587</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="75">
         <f>'건설계획표_26~38'!J30</f>
         <v>392.27395921118011</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="75">
         <f>'건설계획표_26~38'!K30</f>
         <v>398.57621666583145</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="75">
         <f>'건설계획표_26~38'!L30</f>
         <v>488.17770801325815</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="75">
         <f>'건설계획표_26~38'!M30</f>
         <v>405.68726544899846</v>
       </c>
-      <c r="T7" s="76">
+      <c r="T7" s="75">
         <f>'건설계획표_26~38'!N30</f>
         <v>409.80066147219389</v>
       </c>
-      <c r="U7" s="76">
+      <c r="U7" s="75">
         <f>'건설계획표_26~38'!O30</f>
         <v>411.83862611988224</v>
       </c>
-      <c r="V7" s="76">
+      <c r="V7" s="75">
         <f>'건설계획표_26~38'!P30</f>
         <v>0</v>
       </c>
-      <c r="W7" s="76">
+      <c r="W7" s="75">
         <f>'건설계획표_26~38'!Q30</f>
         <v>0</v>
       </c>
-      <c r="X7" s="76">
+      <c r="X7" s="75">
         <f>'건설계획표_26~38'!R30</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="76">
+      <c r="Y7" s="75">
         <f>'건설계획표_26~38'!S30</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="76">
+      <c r="Z7" s="75">
         <f>'건설계획표_26~38'!T30</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="76">
+      <c r="AA7" s="75">
         <f>'건설계획표_26~38'!U30</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="76">
+      <c r="AB7" s="75">
         <f>'건설계획표_26~38'!V30</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="76">
+      <c r="AC7" s="75">
         <f>'건설계획표_26~38'!W30</f>
         <v>0</v>
       </c>
-      <c r="AD7" s="76">
+      <c r="AD7" s="75">
         <f>'건설계획표_26~38'!X30</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="76">
+      <c r="AE7" s="75">
         <f>'건설계획표_26~38'!Y30</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="76">
+      <c r="AF7" s="75">
         <f>'건설계획표_26~38'!Z30</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="76">
+      <c r="AG7" s="75">
         <f>'건설계획표_26~38'!AA30</f>
         <v>0</v>
       </c>
@@ -10712,131 +11020,131 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="76">
+      <c r="B8" s="75">
         <f>'설비현황_19~25'!B31</f>
         <v>0</v>
       </c>
-      <c r="C8" s="76">
+      <c r="C8" s="75">
         <f>'설비현황_19~25'!C31</f>
-        <v>4095.5200000000004</v>
-      </c>
-      <c r="D8" s="76">
+        <v>4237.8089999999993</v>
+      </c>
+      <c r="D8" s="75">
         <f>'설비현황_19~25'!D31</f>
-        <v>3956.1799999999985</v>
-      </c>
-      <c r="E8" s="76">
+        <v>3427.4629999999997</v>
+      </c>
+      <c r="E8" s="75">
         <f>'설비현황_19~25'!E31</f>
-        <v>2986.2900000000009</v>
-      </c>
-      <c r="F8" s="76">
+        <v>2712.8480000000018</v>
+      </c>
+      <c r="F8" s="75">
         <f>'설비현황_19~25'!F31</f>
-        <v>2745.380000000001</v>
-      </c>
-      <c r="G8" s="76">
+        <v>3134.84</v>
+      </c>
+      <c r="G8" s="75">
         <f>'설비현황_19~25'!G31</f>
-        <v>5568.369999999999</v>
-      </c>
-      <c r="H8" s="76">
+        <v>3196.2259999999987</v>
+      </c>
+      <c r="H8" s="75">
         <f>'설비현황_19~25'!H31</f>
         <v>3814</v>
       </c>
-      <c r="I8" s="76">
+      <c r="I8" s="75">
         <f>'건설계획표_26~38'!C31</f>
         <v>4126</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="75">
         <f>'건설계획표_26~38'!D31</f>
         <v>4327</v>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="75">
         <f>'건설계획표_26~38'!E31</f>
         <v>4405</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="75">
         <f>'건설계획표_26~38'!F31</f>
         <v>4450</v>
       </c>
-      <c r="M8" s="76">
+      <c r="M8" s="75">
         <f>'건설계획표_26~38'!G31</f>
         <v>6403</v>
       </c>
-      <c r="N8" s="76">
+      <c r="N8" s="75">
         <f>'건설계획표_26~38'!H31</f>
         <v>3036</v>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="75">
         <f>'건설계획표_26~38'!I31</f>
         <v>3028</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="75">
         <f>'건설계획표_26~38'!J31</f>
         <v>3024</v>
       </c>
-      <c r="Q8" s="76">
+      <c r="Q8" s="75">
         <f>'건설계획표_26~38'!K31</f>
         <v>3021</v>
       </c>
-      <c r="R8" s="76">
+      <c r="R8" s="75">
         <f>'건설계획표_26~38'!L31</f>
         <v>3027</v>
       </c>
-      <c r="S8" s="76">
+      <c r="S8" s="75">
         <f>'건설계획표_26~38'!M31</f>
         <v>2130</v>
       </c>
-      <c r="T8" s="76">
+      <c r="T8" s="75">
         <f>'건설계획표_26~38'!N31</f>
         <v>2131</v>
       </c>
-      <c r="U8" s="76">
+      <c r="U8" s="75">
         <f>'건설계획표_26~38'!O31</f>
         <v>2131</v>
       </c>
-      <c r="V8" s="76">
+      <c r="V8" s="75">
         <f>'건설계획표_26~38'!P31</f>
         <v>0</v>
       </c>
-      <c r="W8" s="76">
+      <c r="W8" s="75">
         <f>'건설계획표_26~38'!Q31</f>
         <v>0</v>
       </c>
-      <c r="X8" s="76">
+      <c r="X8" s="75">
         <f>'건설계획표_26~38'!R31</f>
         <v>0</v>
       </c>
-      <c r="Y8" s="76">
+      <c r="Y8" s="75">
         <f>'건설계획표_26~38'!S31</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="76">
+      <c r="Z8" s="75">
         <f>'건설계획표_26~38'!T31</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="76">
+      <c r="AA8" s="75">
         <f>'건설계획표_26~38'!U31</f>
         <v>0</v>
       </c>
-      <c r="AB8" s="76">
+      <c r="AB8" s="75">
         <f>'건설계획표_26~38'!V31</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="76">
+      <c r="AC8" s="75">
         <f>'건설계획표_26~38'!W31</f>
         <v>0</v>
       </c>
-      <c r="AD8" s="76">
+      <c r="AD8" s="75">
         <f>'건설계획표_26~38'!X31</f>
         <v>0</v>
       </c>
-      <c r="AE8" s="76">
+      <c r="AE8" s="75">
         <f>'건설계획표_26~38'!Y31</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="76">
+      <c r="AF8" s="75">
         <f>'건설계획표_26~38'!Z31</f>
         <v>0</v>
       </c>
-      <c r="AG8" s="76">
+      <c r="AG8" s="75">
         <f>'건설계획표_26~38'!AA31</f>
         <v>0</v>
       </c>
@@ -10845,131 +11153,131 @@
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="75">
         <f>'설비현황_19~25'!B32</f>
         <v>0</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="75">
         <f>'설비현황_19~25'!C32</f>
         <v>0</v>
       </c>
-      <c r="D9" s="76">
+      <c r="D9" s="75">
         <f>'설비현황_19~25'!D32</f>
         <v>0</v>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="75">
         <f>'설비현황_19~25'!E32</f>
         <v>0</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="75">
         <f>'설비현황_19~25'!F32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="75">
         <f>'설비현황_19~25'!G32</f>
         <v>0</v>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="75">
         <f>'설비현황_19~25'!H32</f>
         <v>0</v>
       </c>
-      <c r="I9" s="76">
+      <c r="I9" s="75">
         <f>'건설계획표_26~38'!C32</f>
         <v>0</v>
       </c>
-      <c r="J9" s="76">
+      <c r="J9" s="75">
         <f>'건설계획표_26~38'!D32</f>
         <v>0</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="75">
         <f>'건설계획표_26~38'!E32</f>
         <v>0</v>
       </c>
-      <c r="L9" s="76">
+      <c r="L9" s="75">
         <f>'건설계획표_26~38'!F32</f>
         <v>0</v>
       </c>
-      <c r="M9" s="76">
+      <c r="M9" s="75">
         <f>'건설계획표_26~38'!G32</f>
         <v>0</v>
       </c>
-      <c r="N9" s="76">
+      <c r="N9" s="75">
         <f>'건설계획표_26~38'!H32</f>
         <v>0</v>
       </c>
-      <c r="O9" s="76">
+      <c r="O9" s="75">
         <f>'건설계획표_26~38'!I32</f>
         <v>0</v>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="75">
         <f>'건설계획표_26~38'!J32</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="76">
+      <c r="Q9" s="75">
         <f>'건설계획표_26~38'!K32</f>
         <v>0</v>
       </c>
-      <c r="R9" s="76">
+      <c r="R9" s="75">
         <f>'건설계획표_26~38'!L32</f>
         <v>0</v>
       </c>
-      <c r="S9" s="76">
+      <c r="S9" s="75">
         <f>'건설계획표_26~38'!M32</f>
         <v>0</v>
       </c>
-      <c r="T9" s="76">
+      <c r="T9" s="75">
         <f>'건설계획표_26~38'!N32</f>
         <v>0</v>
       </c>
-      <c r="U9" s="76">
+      <c r="U9" s="75">
         <f>'건설계획표_26~38'!O32</f>
         <v>0</v>
       </c>
-      <c r="V9" s="76">
+      <c r="V9" s="75">
         <f>'건설계획표_26~38'!P32</f>
         <v>0</v>
       </c>
-      <c r="W9" s="76">
+      <c r="W9" s="75">
         <f>'건설계획표_26~38'!Q32</f>
         <v>0</v>
       </c>
-      <c r="X9" s="76">
+      <c r="X9" s="75">
         <f>'건설계획표_26~38'!R32</f>
         <v>0</v>
       </c>
-      <c r="Y9" s="76">
+      <c r="Y9" s="75">
         <f>'건설계획표_26~38'!S32</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="76">
+      <c r="Z9" s="75">
         <f>'건설계획표_26~38'!T32</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="76">
+      <c r="AA9" s="75">
         <f>'건설계획표_26~38'!U32</f>
         <v>0</v>
       </c>
-      <c r="AB9" s="76">
+      <c r="AB9" s="75">
         <f>'건설계획표_26~38'!V32</f>
         <v>0</v>
       </c>
-      <c r="AC9" s="76">
+      <c r="AC9" s="75">
         <f>'건설계획표_26~38'!W32</f>
         <v>0</v>
       </c>
-      <c r="AD9" s="76">
+      <c r="AD9" s="75">
         <f>'건설계획표_26~38'!X32</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="76">
+      <c r="AE9" s="75">
         <f>'건설계획표_26~38'!Y32</f>
         <v>0</v>
       </c>
-      <c r="AF9" s="76">
+      <c r="AF9" s="75">
         <f>'건설계획표_26~38'!Z32</f>
         <v>0</v>
       </c>
-      <c r="AG9" s="76">
+      <c r="AG9" s="75">
         <f>'건설계획표_26~38'!AA32</f>
         <v>0</v>
       </c>
@@ -10978,130 +11286,130 @@
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="76">
+      <c r="B10" s="75">
         <f>'설비현황_19~25'!B33</f>
         <v>0</v>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="75">
         <f>'설비현황_19~25'!C33</f>
         <v>0</v>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="75">
         <v>124.044</v>
       </c>
-      <c r="E10" s="76">
+      <c r="E10" s="75">
         <f>'설비현황_19~25'!E33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="75">
         <f>'설비현황_19~25'!F33</f>
         <v>0</v>
       </c>
-      <c r="G10" s="76">
+      <c r="G10" s="75">
         <f>'설비현황_19~25'!G33</f>
         <v>0</v>
       </c>
-      <c r="H10" s="76">
+      <c r="H10" s="75">
         <f>'설비현황_19~25'!H33</f>
         <v>0</v>
       </c>
-      <c r="I10" s="76">
+      <c r="I10" s="75">
         <f>'건설계획표_26~38'!C33</f>
         <v>0</v>
       </c>
-      <c r="J10" s="76">
+      <c r="J10" s="75">
         <f>'건설계획표_26~38'!D33</f>
         <v>0</v>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="75">
         <f>'건설계획표_26~38'!E33</f>
         <v>0</v>
       </c>
-      <c r="L10" s="76">
+      <c r="L10" s="75">
         <f>'건설계획표_26~38'!F33</f>
         <v>0</v>
       </c>
-      <c r="M10" s="76">
+      <c r="M10" s="75">
         <f>'건설계획표_26~38'!G33</f>
         <v>0</v>
       </c>
-      <c r="N10" s="76">
+      <c r="N10" s="75">
         <f>'건설계획표_26~38'!H33</f>
         <v>0</v>
       </c>
-      <c r="O10" s="76">
+      <c r="O10" s="75">
         <f>'건설계획표_26~38'!I33</f>
         <v>0</v>
       </c>
-      <c r="P10" s="76">
+      <c r="P10" s="75">
         <f>'건설계획표_26~38'!J33</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="76">
+      <c r="Q10" s="75">
         <f>'건설계획표_26~38'!K33</f>
         <v>0</v>
       </c>
-      <c r="R10" s="76">
+      <c r="R10" s="75">
         <f>'건설계획표_26~38'!L33</f>
         <v>0</v>
       </c>
-      <c r="S10" s="76">
+      <c r="S10" s="75">
         <f>'건설계획표_26~38'!M33</f>
         <v>0</v>
       </c>
-      <c r="T10" s="76">
+      <c r="T10" s="75">
         <f>'건설계획표_26~38'!N33</f>
         <v>0</v>
       </c>
-      <c r="U10" s="76">
+      <c r="U10" s="75">
         <f>'건설계획표_26~38'!O33</f>
         <v>0</v>
       </c>
-      <c r="V10" s="76">
+      <c r="V10" s="75">
         <f>'건설계획표_26~38'!P33</f>
         <v>0</v>
       </c>
-      <c r="W10" s="76">
+      <c r="W10" s="75">
         <f>'건설계획표_26~38'!Q33</f>
         <v>0</v>
       </c>
-      <c r="X10" s="76">
+      <c r="X10" s="75">
         <f>'건설계획표_26~38'!R33</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="76">
+      <c r="Y10" s="75">
         <f>'건설계획표_26~38'!S33</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="76">
+      <c r="Z10" s="75">
         <f>'건설계획표_26~38'!T33</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="76">
+      <c r="AA10" s="75">
         <f>'건설계획표_26~38'!U33</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="76">
+      <c r="AB10" s="75">
         <f>'건설계획표_26~38'!V33</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="76">
+      <c r="AC10" s="75">
         <f>'건설계획표_26~38'!W33</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="76">
+      <c r="AD10" s="75">
         <f>'건설계획표_26~38'!X33</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="76">
+      <c r="AE10" s="75">
         <f>'건설계획표_26~38'!Y33</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="76">
+      <c r="AF10" s="75">
         <f>'건설계획표_26~38'!Z33</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="76">
+      <c r="AG10" s="75">
         <f>'건설계획표_26~38'!AA33</f>
         <v>0</v>
       </c>
@@ -11110,131 +11418,131 @@
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="76">
+      <c r="B11" s="75">
         <f>'설비현황_19~25'!B34</f>
         <v>0</v>
       </c>
-      <c r="C11" s="76">
+      <c r="C11" s="75">
         <f>'설비현황_19~25'!C34</f>
         <v>0</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="75">
         <f>'설비현황_19~25'!D34</f>
         <v>0</v>
       </c>
-      <c r="E11" s="76">
+      <c r="E11" s="75">
         <f>'설비현황_19~25'!E34</f>
         <v>0</v>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="75">
         <f>'설비현황_19~25'!F34</f>
         <v>0</v>
       </c>
-      <c r="G11" s="76">
+      <c r="G11" s="75">
         <f>'설비현황_19~25'!G34</f>
         <v>0</v>
       </c>
-      <c r="H11" s="76">
+      <c r="H11" s="75">
         <f>'설비현황_19~25'!H34</f>
         <v>0</v>
       </c>
-      <c r="I11" s="76">
+      <c r="I11" s="75">
         <f>'건설계획표_26~38'!C34</f>
         <v>0</v>
       </c>
-      <c r="J11" s="76">
+      <c r="J11" s="75">
         <f>'건설계획표_26~38'!D34</f>
         <v>0</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="75">
         <f>'건설계획표_26~38'!E34</f>
         <v>0</v>
       </c>
-      <c r="L11" s="76">
+      <c r="L11" s="75">
         <f>'건설계획표_26~38'!F34</f>
         <v>0</v>
       </c>
-      <c r="M11" s="76">
+      <c r="M11" s="75">
         <f>'건설계획표_26~38'!G34</f>
         <v>0</v>
       </c>
-      <c r="N11" s="76">
+      <c r="N11" s="75">
         <f>'건설계획표_26~38'!H34</f>
         <v>0</v>
       </c>
-      <c r="O11" s="76">
+      <c r="O11" s="75">
         <f>'건설계획표_26~38'!I34</f>
         <v>0</v>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="75">
         <f>'건설계획표_26~38'!J34</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="76">
+      <c r="Q11" s="75">
         <f>'건설계획표_26~38'!K34</f>
         <v>0</v>
       </c>
-      <c r="R11" s="76">
+      <c r="R11" s="75">
         <f>'건설계획표_26~38'!L34</f>
         <v>0</v>
       </c>
-      <c r="S11" s="76">
+      <c r="S11" s="75">
         <f>'건설계획표_26~38'!M34</f>
         <v>0</v>
       </c>
-      <c r="T11" s="76">
+      <c r="T11" s="75">
         <f>'건설계획표_26~38'!N34</f>
         <v>0</v>
       </c>
-      <c r="U11" s="76">
+      <c r="U11" s="75">
         <f>'건설계획표_26~38'!O34</f>
         <v>0</v>
       </c>
-      <c r="V11" s="76">
+      <c r="V11" s="75">
         <f>'건설계획표_26~38'!P34</f>
         <v>0</v>
       </c>
-      <c r="W11" s="76">
+      <c r="W11" s="75">
         <f>'건설계획표_26~38'!Q34</f>
         <v>0</v>
       </c>
-      <c r="X11" s="76">
+      <c r="X11" s="75">
         <f>'건설계획표_26~38'!R34</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="76">
+      <c r="Y11" s="75">
         <f>'건설계획표_26~38'!S34</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="76">
+      <c r="Z11" s="75">
         <f>'건설계획표_26~38'!T34</f>
         <v>0</v>
       </c>
-      <c r="AA11" s="76">
+      <c r="AA11" s="75">
         <f>'건설계획표_26~38'!U34</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="76">
+      <c r="AB11" s="75">
         <f>'건설계획표_26~38'!V34</f>
         <v>0</v>
       </c>
-      <c r="AC11" s="76">
+      <c r="AC11" s="75">
         <f>'건설계획표_26~38'!W34</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="76">
+      <c r="AD11" s="75">
         <f>'건설계획표_26~38'!X34</f>
         <v>0</v>
       </c>
-      <c r="AE11" s="76">
+      <c r="AE11" s="75">
         <f>'건설계획표_26~38'!Y34</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="76">
+      <c r="AF11" s="75">
         <f>'건설계획표_26~38'!Z34</f>
         <v>0</v>
       </c>
-      <c r="AG11" s="76">
+      <c r="AG11" s="75">
         <f>'건설계획표_26~38'!AA34</f>
         <v>0</v>
       </c>
@@ -11243,131 +11551,131 @@
       <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="76">
+      <c r="B12" s="75">
         <f>'설비현황_19~25'!B35</f>
         <v>0</v>
       </c>
-      <c r="C12" s="76">
+      <c r="C12" s="75">
         <f>'설비현황_19~25'!C35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="76">
+      <c r="D12" s="75">
         <f>'설비현황_19~25'!D35</f>
         <v>0</v>
       </c>
-      <c r="E12" s="76">
+      <c r="E12" s="75">
         <f>'설비현황_19~25'!E35</f>
         <v>0</v>
       </c>
-      <c r="F12" s="76">
+      <c r="F12" s="75">
         <f>'설비현황_19~25'!F35</f>
         <v>0</v>
       </c>
-      <c r="G12" s="76">
+      <c r="G12" s="75">
         <f>'설비현황_19~25'!G35</f>
         <v>0</v>
       </c>
-      <c r="H12" s="76">
+      <c r="H12" s="75">
         <f>'설비현황_19~25'!H35</f>
         <v>0</v>
       </c>
-      <c r="I12" s="76">
+      <c r="I12" s="75">
         <f>'건설계획표_26~38'!C35</f>
         <v>0</v>
       </c>
-      <c r="J12" s="76">
+      <c r="J12" s="75">
         <f>'건설계획표_26~38'!D35</f>
         <v>0</v>
       </c>
-      <c r="K12" s="76">
+      <c r="K12" s="75">
         <f>'건설계획표_26~38'!E35</f>
         <v>0</v>
       </c>
-      <c r="L12" s="76">
+      <c r="L12" s="75">
         <f>'건설계획표_26~38'!F35</f>
         <v>0</v>
       </c>
-      <c r="M12" s="76">
+      <c r="M12" s="75">
         <f>'건설계획표_26~38'!G35</f>
         <v>0</v>
       </c>
-      <c r="N12" s="76">
+      <c r="N12" s="75">
         <f>'건설계획표_26~38'!H35</f>
         <v>0</v>
       </c>
-      <c r="O12" s="76">
+      <c r="O12" s="75">
         <f>'건설계획표_26~38'!I35</f>
         <v>0</v>
       </c>
-      <c r="P12" s="76">
+      <c r="P12" s="75">
         <f>'건설계획표_26~38'!J35</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="76">
+      <c r="Q12" s="75">
         <f>'건설계획표_26~38'!K35</f>
         <v>0</v>
       </c>
-      <c r="R12" s="76">
+      <c r="R12" s="75">
         <f>'건설계획표_26~38'!L35</f>
         <v>0</v>
       </c>
-      <c r="S12" s="76">
+      <c r="S12" s="75">
         <f>'건설계획표_26~38'!M35</f>
         <v>0</v>
       </c>
-      <c r="T12" s="76">
+      <c r="T12" s="75">
         <f>'건설계획표_26~38'!N35</f>
         <v>0</v>
       </c>
-      <c r="U12" s="76">
+      <c r="U12" s="75">
         <f>'건설계획표_26~38'!O35</f>
         <v>0</v>
       </c>
-      <c r="V12" s="76">
+      <c r="V12" s="75">
         <f>'건설계획표_26~38'!P35</f>
         <v>0</v>
       </c>
-      <c r="W12" s="76">
+      <c r="W12" s="75">
         <f>'건설계획표_26~38'!Q35</f>
         <v>0</v>
       </c>
-      <c r="X12" s="76">
+      <c r="X12" s="75">
         <f>'건설계획표_26~38'!R35</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="76">
+      <c r="Y12" s="75">
         <f>'건설계획표_26~38'!S35</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="76">
+      <c r="Z12" s="75">
         <f>'건설계획표_26~38'!T35</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="76">
+      <c r="AA12" s="75">
         <f>'건설계획표_26~38'!U35</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="76">
+      <c r="AB12" s="75">
         <f>'건설계획표_26~38'!V35</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="76">
+      <c r="AC12" s="75">
         <f>'건설계획표_26~38'!W35</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="76">
+      <c r="AD12" s="75">
         <f>'건설계획표_26~38'!X35</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="76">
+      <c r="AE12" s="75">
         <f>'건설계획표_26~38'!Y35</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="76">
+      <c r="AF12" s="75">
         <f>'건설계획표_26~38'!Z35</f>
         <v>0</v>
       </c>
-      <c r="AG12" s="76">
+      <c r="AG12" s="75">
         <f>'건설계획표_26~38'!AA35</f>
         <v>0</v>
       </c>
@@ -11376,131 +11684,131 @@
       <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="76">
+      <c r="B13" s="75">
         <f>'설비현황_19~25'!B36</f>
         <v>0</v>
       </c>
-      <c r="C13" s="76">
+      <c r="C13" s="75">
         <f>'설비현황_19~25'!C36</f>
         <v>0</v>
       </c>
-      <c r="D13" s="76">
+      <c r="D13" s="75">
         <f>'설비현황_19~25'!D36</f>
         <v>0</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="75">
         <f>'설비현황_19~25'!E36</f>
         <v>0</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="75">
         <f>'설비현황_19~25'!F36</f>
         <v>0</v>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="75">
         <f>'설비현황_19~25'!G36</f>
         <v>0</v>
       </c>
-      <c r="H13" s="76">
+      <c r="H13" s="75">
         <f>'설비현황_19~25'!H36</f>
         <v>0</v>
       </c>
-      <c r="I13" s="76">
+      <c r="I13" s="75">
         <f>'건설계획표_26~38'!C36</f>
         <v>0</v>
       </c>
-      <c r="J13" s="76">
+      <c r="J13" s="75">
         <f>'건설계획표_26~38'!D36</f>
         <v>0</v>
       </c>
-      <c r="K13" s="76">
+      <c r="K13" s="75">
         <f>'건설계획표_26~38'!E36</f>
         <v>0</v>
       </c>
-      <c r="L13" s="76">
+      <c r="L13" s="75">
         <f>'건설계획표_26~38'!F36</f>
         <v>0</v>
       </c>
-      <c r="M13" s="76">
+      <c r="M13" s="75">
         <f>'건설계획표_26~38'!G36</f>
         <v>0</v>
       </c>
-      <c r="N13" s="76">
+      <c r="N13" s="75">
         <f>'건설계획표_26~38'!H36</f>
         <v>0</v>
       </c>
-      <c r="O13" s="76">
+      <c r="O13" s="75">
         <f>'건설계획표_26~38'!I36</f>
         <v>0</v>
       </c>
-      <c r="P13" s="76">
+      <c r="P13" s="75">
         <f>'건설계획표_26~38'!J36</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="76">
+      <c r="Q13" s="75">
         <f>'건설계획표_26~38'!K36</f>
         <v>0</v>
       </c>
-      <c r="R13" s="76">
+      <c r="R13" s="75">
         <f>'건설계획표_26~38'!L36</f>
         <v>0</v>
       </c>
-      <c r="S13" s="76">
+      <c r="S13" s="75">
         <f>'건설계획표_26~38'!M36</f>
         <v>0</v>
       </c>
-      <c r="T13" s="76">
+      <c r="T13" s="75">
         <f>'건설계획표_26~38'!N36</f>
         <v>0</v>
       </c>
-      <c r="U13" s="76">
+      <c r="U13" s="75">
         <f>'건설계획표_26~38'!O36</f>
         <v>0</v>
       </c>
-      <c r="V13" s="76">
+      <c r="V13" s="75">
         <f>'건설계획표_26~38'!P36</f>
         <v>0</v>
       </c>
-      <c r="W13" s="76">
+      <c r="W13" s="75">
         <f>'건설계획표_26~38'!Q36</f>
         <v>0</v>
       </c>
-      <c r="X13" s="76">
+      <c r="X13" s="75">
         <f>'건설계획표_26~38'!R36</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="76">
+      <c r="Y13" s="75">
         <f>'건설계획표_26~38'!S36</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="76">
+      <c r="Z13" s="75">
         <f>'건설계획표_26~38'!T36</f>
         <v>0</v>
       </c>
-      <c r="AA13" s="76">
+      <c r="AA13" s="75">
         <f>'건설계획표_26~38'!U36</f>
         <v>0</v>
       </c>
-      <c r="AB13" s="76">
+      <c r="AB13" s="75">
         <f>'건설계획표_26~38'!V36</f>
         <v>0</v>
       </c>
-      <c r="AC13" s="76">
+      <c r="AC13" s="75">
         <f>'건설계획표_26~38'!W36</f>
         <v>0</v>
       </c>
-      <c r="AD13" s="76">
+      <c r="AD13" s="75">
         <f>'건설계획표_26~38'!X36</f>
         <v>0</v>
       </c>
-      <c r="AE13" s="76">
+      <c r="AE13" s="75">
         <f>'건설계획표_26~38'!Y36</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="76">
+      <c r="AF13" s="75">
         <f>'건설계획표_26~38'!Z36</f>
         <v>0</v>
       </c>
-      <c r="AG13" s="76">
+      <c r="AG13" s="75">
         <f>'건설계획표_26~38'!AA36</f>
         <v>0</v>
       </c>
@@ -11509,131 +11817,131 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="76">
+      <c r="B14" s="75">
         <f>'설비현황_19~25'!B37</f>
         <v>0</v>
       </c>
-      <c r="C14" s="76">
+      <c r="C14" s="75">
         <f>'설비현황_19~25'!C37</f>
         <v>0</v>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="75">
         <f>'설비현황_19~25'!D37</f>
         <v>0</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="75">
         <f>'설비현황_19~25'!E37</f>
         <v>0</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="75">
         <f>'설비현황_19~25'!F37</f>
         <v>0</v>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="75">
         <f>'설비현황_19~25'!G37</f>
         <v>0</v>
       </c>
-      <c r="H14" s="76">
+      <c r="H14" s="75">
         <f>'설비현황_19~25'!H37</f>
         <v>0</v>
       </c>
-      <c r="I14" s="76">
+      <c r="I14" s="75">
         <f>'건설계획표_26~38'!C37</f>
         <v>0</v>
       </c>
-      <c r="J14" s="76">
+      <c r="J14" s="75">
         <f>'건설계획표_26~38'!D37</f>
         <v>0</v>
       </c>
-      <c r="K14" s="76">
+      <c r="K14" s="75">
         <f>'건설계획표_26~38'!E37</f>
         <v>0</v>
       </c>
-      <c r="L14" s="76">
+      <c r="L14" s="75">
         <f>'건설계획표_26~38'!F37</f>
         <v>0</v>
       </c>
-      <c r="M14" s="76">
+      <c r="M14" s="75">
         <f>'건설계획표_26~38'!G37</f>
         <v>0</v>
       </c>
-      <c r="N14" s="76">
+      <c r="N14" s="75">
         <f>'건설계획표_26~38'!H37</f>
         <v>0</v>
       </c>
-      <c r="O14" s="76">
+      <c r="O14" s="75">
         <f>'건설계획표_26~38'!I37</f>
         <v>0</v>
       </c>
-      <c r="P14" s="76">
+      <c r="P14" s="75">
         <f>'건설계획표_26~38'!J37</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="76">
+      <c r="Q14" s="75">
         <f>'건설계획표_26~38'!K37</f>
         <v>0</v>
       </c>
-      <c r="R14" s="76">
+      <c r="R14" s="75">
         <f>'건설계획표_26~38'!L37</f>
         <v>0</v>
       </c>
-      <c r="S14" s="76">
+      <c r="S14" s="75">
         <f>'건설계획표_26~38'!M37</f>
         <v>0</v>
       </c>
-      <c r="T14" s="76">
+      <c r="T14" s="75">
         <f>'건설계획표_26~38'!N37</f>
         <v>0</v>
       </c>
-      <c r="U14" s="76">
+      <c r="U14" s="75">
         <f>'건설계획표_26~38'!O37</f>
         <v>0</v>
       </c>
-      <c r="V14" s="76">
+      <c r="V14" s="75">
         <f>'건설계획표_26~38'!P37</f>
         <v>0</v>
       </c>
-      <c r="W14" s="76">
+      <c r="W14" s="75">
         <f>'건설계획표_26~38'!Q37</f>
         <v>0</v>
       </c>
-      <c r="X14" s="76">
+      <c r="X14" s="75">
         <f>'건설계획표_26~38'!R37</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="76">
+      <c r="Y14" s="75">
         <f>'건설계획표_26~38'!S37</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="76">
+      <c r="Z14" s="75">
         <f>'건설계획표_26~38'!T37</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="76">
+      <c r="AA14" s="75">
         <f>'건설계획표_26~38'!U37</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="76">
+      <c r="AB14" s="75">
         <f>'건설계획표_26~38'!V37</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="76">
+      <c r="AC14" s="75">
         <f>'건설계획표_26~38'!W37</f>
         <v>0</v>
       </c>
-      <c r="AD14" s="76">
+      <c r="AD14" s="75">
         <f>'건설계획표_26~38'!X37</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="76">
+      <c r="AE14" s="75">
         <f>'건설계획표_26~38'!Y37</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="76">
+      <c r="AF14" s="75">
         <f>'건설계획표_26~38'!Z37</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="76">
+      <c r="AG14" s="75">
         <f>'건설계획표_26~38'!AA37</f>
         <v>0</v>
       </c>
@@ -11642,131 +11950,131 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="76">
+      <c r="B15" s="75">
         <f>'설비현황_19~25'!B38</f>
         <v>0</v>
       </c>
-      <c r="C15" s="76">
+      <c r="C15" s="75">
         <f>'설비현황_19~25'!C38</f>
         <v>60</v>
       </c>
-      <c r="D15" s="76">
+      <c r="D15" s="75">
         <f>'설비현황_19~25'!D38</f>
         <v>0</v>
       </c>
-      <c r="E15" s="76">
+      <c r="E15" s="75">
         <f>'설비현황_19~25'!E38</f>
         <v>0</v>
       </c>
-      <c r="F15" s="76">
+      <c r="F15" s="75">
         <f>'설비현황_19~25'!F38</f>
         <v>26</v>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="75">
         <f>'설비현황_19~25'!G38</f>
         <v>110.32999999999998</v>
       </c>
-      <c r="H15" s="76">
+      <c r="H15" s="75">
         <f>'설비현황_19~25'!H38</f>
         <v>103.30000000000001</v>
       </c>
-      <c r="I15" s="76">
+      <c r="I15" s="75">
         <f>'건설계획표_26~38'!C38</f>
         <v>786.3301407049056</v>
       </c>
-      <c r="J15" s="76">
+      <c r="J15" s="75">
         <f>'건설계획표_26~38'!D38</f>
         <v>1692.1557225582499</v>
       </c>
-      <c r="K15" s="76">
+      <c r="K15" s="75">
         <f>'건설계획표_26~38'!E38</f>
         <v>2286.2903984785771</v>
       </c>
-      <c r="L15" s="76">
+      <c r="L15" s="75">
         <f>'건설계획표_26~38'!F38</f>
         <v>4965.328051082035</v>
       </c>
-      <c r="M15" s="76">
+      <c r="M15" s="75">
         <f>'건설계획표_26~38'!G38</f>
         <v>3024.9894892152415</v>
       </c>
-      <c r="N15" s="76">
+      <c r="N15" s="75">
         <f>'건설계획표_26~38'!H38</f>
         <v>3375.9551205608909</v>
       </c>
-      <c r="O15" s="76">
+      <c r="O15" s="75">
         <f>'건설계획표_26~38'!I38</f>
         <v>2131.8829479001442</v>
       </c>
-      <c r="P15" s="76">
+      <c r="P15" s="75">
         <f>'건설계획표_26~38'!J38</f>
         <v>2158.7260407888198</v>
       </c>
-      <c r="Q15" s="76">
+      <c r="Q15" s="75">
         <f>'건설계획표_26~38'!K38</f>
         <v>2155.4237833341685</v>
       </c>
-      <c r="R15" s="76">
+      <c r="R15" s="75">
         <f>'건설계획표_26~38'!L38</f>
         <v>2510.8222919867421</v>
       </c>
-      <c r="S15" s="76">
+      <c r="S15" s="75">
         <f>'건설계획표_26~38'!M38</f>
         <v>2154.3127345510015</v>
       </c>
-      <c r="T15" s="76">
+      <c r="T15" s="75">
         <f>'건설계획표_26~38'!N38</f>
         <v>2159.199338527806</v>
       </c>
-      <c r="U15" s="76">
+      <c r="U15" s="75">
         <f>'건설계획표_26~38'!O38</f>
         <v>2158.1613738801179</v>
       </c>
-      <c r="V15" s="76">
+      <c r="V15" s="75">
         <f>'건설계획표_26~38'!P38</f>
         <v>0</v>
       </c>
-      <c r="W15" s="76">
+      <c r="W15" s="75">
         <f>'건설계획표_26~38'!Q38</f>
         <v>0</v>
       </c>
-      <c r="X15" s="76">
+      <c r="X15" s="75">
         <f>'건설계획표_26~38'!R38</f>
         <v>0</v>
       </c>
-      <c r="Y15" s="76">
+      <c r="Y15" s="75">
         <f>'건설계획표_26~38'!S38</f>
         <v>0</v>
       </c>
-      <c r="Z15" s="76">
+      <c r="Z15" s="75">
         <f>'건설계획표_26~38'!T38</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="76">
+      <c r="AA15" s="75">
         <f>'건설계획표_26~38'!U38</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="76">
+      <c r="AB15" s="75">
         <f>'건설계획표_26~38'!V38</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="76">
+      <c r="AC15" s="75">
         <f>'건설계획표_26~38'!W38</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="76">
+      <c r="AD15" s="75">
         <f>'건설계획표_26~38'!X38</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="76">
+      <c r="AE15" s="75">
         <f>'건설계획표_26~38'!Y38</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="76">
+      <c r="AF15" s="75">
         <f>'건설계획표_26~38'!Z38</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="76">
+      <c r="AG15" s="75">
         <f>'건설계획표_26~38'!AA38</f>
         <v>0</v>
       </c>
@@ -11775,131 +12083,131 @@
       <c r="A16" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="76">
+      <c r="B16" s="75">
         <f>'설비현황_19~25'!B39</f>
         <v>0</v>
       </c>
-      <c r="C16" s="76">
+      <c r="C16" s="75">
         <f>'설비현황_19~25'!C39</f>
         <v>0</v>
       </c>
-      <c r="D16" s="76">
+      <c r="D16" s="75">
         <f>'설비현황_19~25'!D39</f>
         <v>0</v>
       </c>
-      <c r="E16" s="76">
+      <c r="E16" s="75">
         <f>'설비현황_19~25'!E39</f>
         <v>0</v>
       </c>
-      <c r="F16" s="76">
+      <c r="F16" s="75">
         <f>'설비현황_19~25'!F39</f>
         <v>0</v>
       </c>
-      <c r="G16" s="76">
+      <c r="G16" s="75">
         <f>'설비현황_19~25'!G39</f>
         <v>0</v>
       </c>
-      <c r="H16" s="76">
+      <c r="H16" s="75">
         <f>'설비현황_19~25'!H39</f>
         <v>0</v>
       </c>
-      <c r="I16" s="76">
+      <c r="I16" s="75">
         <f>'건설계획표_26~38'!C39</f>
         <v>0</v>
       </c>
-      <c r="J16" s="76">
+      <c r="J16" s="75">
         <f>'건설계획표_26~38'!D39</f>
         <v>0</v>
       </c>
-      <c r="K16" s="76">
+      <c r="K16" s="75">
         <f>'건설계획표_26~38'!E39</f>
         <v>0</v>
       </c>
-      <c r="L16" s="76">
+      <c r="L16" s="75">
         <f>'건설계획표_26~38'!F39</f>
         <v>0</v>
       </c>
-      <c r="M16" s="76">
+      <c r="M16" s="75">
         <f>'건설계획표_26~38'!G39</f>
         <v>0</v>
       </c>
-      <c r="N16" s="76">
+      <c r="N16" s="75">
         <f>'건설계획표_26~38'!H39</f>
         <v>0</v>
       </c>
-      <c r="O16" s="76">
+      <c r="O16" s="75">
         <f>'건설계획표_26~38'!I39</f>
         <v>0</v>
       </c>
-      <c r="P16" s="76">
+      <c r="P16" s="75">
         <f>'건설계획표_26~38'!J39</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="76">
+      <c r="Q16" s="75">
         <f>'건설계획표_26~38'!K39</f>
         <v>0</v>
       </c>
-      <c r="R16" s="76">
+      <c r="R16" s="75">
         <f>'건설계획표_26~38'!L39</f>
         <v>0</v>
       </c>
-      <c r="S16" s="76">
+      <c r="S16" s="75">
         <f>'건설계획표_26~38'!M39</f>
         <v>0</v>
       </c>
-      <c r="T16" s="76">
+      <c r="T16" s="75">
         <f>'건설계획표_26~38'!N39</f>
         <v>0</v>
       </c>
-      <c r="U16" s="76">
+      <c r="U16" s="75">
         <f>'건설계획표_26~38'!O39</f>
         <v>0</v>
       </c>
-      <c r="V16" s="76">
+      <c r="V16" s="75">
         <f>'건설계획표_26~38'!P39</f>
         <v>0</v>
       </c>
-      <c r="W16" s="76">
+      <c r="W16" s="75">
         <f>'건설계획표_26~38'!Q39</f>
         <v>0</v>
       </c>
-      <c r="X16" s="76">
+      <c r="X16" s="75">
         <f>'건설계획표_26~38'!R39</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="76">
+      <c r="Y16" s="75">
         <f>'건설계획표_26~38'!S39</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="76">
+      <c r="Z16" s="75">
         <f>'건설계획표_26~38'!T39</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="76">
+      <c r="AA16" s="75">
         <f>'건설계획표_26~38'!U39</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="76">
+      <c r="AB16" s="75">
         <f>'건설계획표_26~38'!V39</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="76">
+      <c r="AC16" s="75">
         <f>'건설계획표_26~38'!W39</f>
         <v>0</v>
       </c>
-      <c r="AD16" s="76">
+      <c r="AD16" s="75">
         <f>'건설계획표_26~38'!X39</f>
         <v>0</v>
       </c>
-      <c r="AE16" s="76">
+      <c r="AE16" s="75">
         <f>'건설계획표_26~38'!Y39</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="76">
+      <c r="AF16" s="75">
         <f>'건설계획표_26~38'!Z39</f>
         <v>0</v>
       </c>
-      <c r="AG16" s="76">
+      <c r="AG16" s="75">
         <f>'건설계획표_26~38'!AA39</f>
         <v>0</v>
       </c>
@@ -11908,131 +12216,131 @@
       <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="76">
+      <c r="B17" s="75">
         <f>'설비현황_19~25'!B40</f>
         <v>0</v>
       </c>
-      <c r="C17" s="76">
+      <c r="C17" s="75">
         <f>'설비현황_19~25'!C40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="76">
+      <c r="D17" s="75">
         <f>'설비현황_19~25'!D40</f>
         <v>0</v>
       </c>
-      <c r="E17" s="76">
+      <c r="E17" s="75">
         <f>'설비현황_19~25'!E40</f>
         <v>0</v>
       </c>
-      <c r="F17" s="76">
+      <c r="F17" s="75">
         <f>'설비현황_19~25'!F40</f>
         <v>0</v>
       </c>
-      <c r="G17" s="76">
+      <c r="G17" s="75">
         <f>'설비현황_19~25'!G40</f>
         <v>0</v>
       </c>
-      <c r="H17" s="76">
+      <c r="H17" s="75">
         <f>'설비현황_19~25'!H40</f>
         <v>0</v>
       </c>
-      <c r="I17" s="76">
+      <c r="I17" s="75">
         <f>'건설계획표_26~38'!C40</f>
         <v>0</v>
       </c>
-      <c r="J17" s="76">
+      <c r="J17" s="75">
         <f>'건설계획표_26~38'!D40</f>
         <v>0</v>
       </c>
-      <c r="K17" s="76">
+      <c r="K17" s="75">
         <f>'건설계획표_26~38'!E40</f>
         <v>0</v>
       </c>
-      <c r="L17" s="76">
+      <c r="L17" s="75">
         <f>'건설계획표_26~38'!F40</f>
         <v>0</v>
       </c>
-      <c r="M17" s="76">
+      <c r="M17" s="75">
         <f>'건설계획표_26~38'!G40</f>
         <v>0</v>
       </c>
-      <c r="N17" s="76">
+      <c r="N17" s="75">
         <f>'건설계획표_26~38'!H40</f>
         <v>0</v>
       </c>
-      <c r="O17" s="76">
+      <c r="O17" s="75">
         <f>'건설계획표_26~38'!I40</f>
         <v>0</v>
       </c>
-      <c r="P17" s="76">
+      <c r="P17" s="75">
         <f>'건설계획표_26~38'!J40</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="76">
+      <c r="Q17" s="75">
         <f>'건설계획표_26~38'!K40</f>
         <v>0</v>
       </c>
-      <c r="R17" s="76">
+      <c r="R17" s="75">
         <f>'건설계획표_26~38'!L40</f>
         <v>0</v>
       </c>
-      <c r="S17" s="76">
+      <c r="S17" s="75">
         <f>'건설계획표_26~38'!M40</f>
         <v>0</v>
       </c>
-      <c r="T17" s="76">
+      <c r="T17" s="75">
         <f>'건설계획표_26~38'!N40</f>
         <v>0</v>
       </c>
-      <c r="U17" s="76">
+      <c r="U17" s="75">
         <f>'건설계획표_26~38'!O40</f>
         <v>0</v>
       </c>
-      <c r="V17" s="76">
+      <c r="V17" s="75">
         <f>'건설계획표_26~38'!P40</f>
         <v>0</v>
       </c>
-      <c r="W17" s="76">
+      <c r="W17" s="75">
         <f>'건설계획표_26~38'!Q40</f>
         <v>0</v>
       </c>
-      <c r="X17" s="76">
+      <c r="X17" s="75">
         <f>'건설계획표_26~38'!R40</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="76">
+      <c r="Y17" s="75">
         <f>'건설계획표_26~38'!S40</f>
         <v>0</v>
       </c>
-      <c r="Z17" s="76">
+      <c r="Z17" s="75">
         <f>'건설계획표_26~38'!T40</f>
         <v>0</v>
       </c>
-      <c r="AA17" s="76">
+      <c r="AA17" s="75">
         <f>'건설계획표_26~38'!U40</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="76">
+      <c r="AB17" s="75">
         <f>'건설계획표_26~38'!V40</f>
         <v>0</v>
       </c>
-      <c r="AC17" s="76">
+      <c r="AC17" s="75">
         <f>'건설계획표_26~38'!W40</f>
         <v>0</v>
       </c>
-      <c r="AD17" s="76">
+      <c r="AD17" s="75">
         <f>'건설계획표_26~38'!X40</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="76">
+      <c r="AE17" s="75">
         <f>'건설계획표_26~38'!Y40</f>
         <v>0</v>
       </c>
-      <c r="AF17" s="76">
+      <c r="AF17" s="75">
         <f>'건설계획표_26~38'!Z40</f>
         <v>0</v>
       </c>
-      <c r="AG17" s="76">
+      <c r="AG17" s="75">
         <f>'건설계획표_26~38'!AA40</f>
         <v>0</v>
       </c>
@@ -12041,131 +12349,131 @@
       <c r="A18" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="76">
+      <c r="B18" s="75">
         <f>'설비현황_19~25'!B41</f>
         <v>0</v>
       </c>
-      <c r="C18" s="76">
+      <c r="C18" s="75">
         <f>'설비현황_19~25'!C41</f>
         <v>0</v>
       </c>
-      <c r="D18" s="76">
+      <c r="D18" s="75">
         <f>'설비현황_19~25'!D41</f>
         <v>0</v>
       </c>
-      <c r="E18" s="76">
+      <c r="E18" s="75">
         <f>'설비현황_19~25'!E41</f>
         <v>0</v>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="75">
         <f>'설비현황_19~25'!F41</f>
         <v>0</v>
       </c>
-      <c r="G18" s="76">
+      <c r="G18" s="75">
         <f>'설비현황_19~25'!G41</f>
         <v>0</v>
       </c>
-      <c r="H18" s="76">
+      <c r="H18" s="75">
         <f>'설비현황_19~25'!H41</f>
         <v>0</v>
       </c>
-      <c r="I18" s="76">
+      <c r="I18" s="75">
         <f>'건설계획표_26~38'!C41</f>
         <v>0</v>
       </c>
-      <c r="J18" s="76">
+      <c r="J18" s="75">
         <f>'건설계획표_26~38'!D41</f>
         <v>0</v>
       </c>
-      <c r="K18" s="76">
+      <c r="K18" s="75">
         <f>'건설계획표_26~38'!E41</f>
         <v>0</v>
       </c>
-      <c r="L18" s="76">
+      <c r="L18" s="75">
         <f>'건설계획표_26~38'!F41</f>
         <v>0</v>
       </c>
-      <c r="M18" s="76">
+      <c r="M18" s="75">
         <f>'건설계획표_26~38'!G41</f>
         <v>0</v>
       </c>
-      <c r="N18" s="76">
+      <c r="N18" s="75">
         <f>'건설계획표_26~38'!H41</f>
         <v>0</v>
       </c>
-      <c r="O18" s="76">
+      <c r="O18" s="75">
         <f>'건설계획표_26~38'!I41</f>
         <v>0</v>
       </c>
-      <c r="P18" s="76">
+      <c r="P18" s="75">
         <f>'건설계획표_26~38'!J41</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="76">
+      <c r="Q18" s="75">
         <f>'건설계획표_26~38'!K41</f>
         <v>0</v>
       </c>
-      <c r="R18" s="76">
+      <c r="R18" s="75">
         <f>'건설계획표_26~38'!L41</f>
         <v>0</v>
       </c>
-      <c r="S18" s="76">
+      <c r="S18" s="75">
         <f>'건설계획표_26~38'!M41</f>
         <v>0</v>
       </c>
-      <c r="T18" s="76">
+      <c r="T18" s="75">
         <f>'건설계획표_26~38'!N41</f>
         <v>0</v>
       </c>
-      <c r="U18" s="76">
+      <c r="U18" s="75">
         <f>'건설계획표_26~38'!O41</f>
         <v>0</v>
       </c>
-      <c r="V18" s="76">
+      <c r="V18" s="75">
         <f>'건설계획표_26~38'!P41</f>
         <v>0</v>
       </c>
-      <c r="W18" s="76">
+      <c r="W18" s="75">
         <f>'건설계획표_26~38'!Q41</f>
         <v>0</v>
       </c>
-      <c r="X18" s="76">
+      <c r="X18" s="75">
         <f>'건설계획표_26~38'!R41</f>
         <v>0</v>
       </c>
-      <c r="Y18" s="76">
+      <c r="Y18" s="75">
         <f>'건설계획표_26~38'!S41</f>
         <v>0</v>
       </c>
-      <c r="Z18" s="76">
+      <c r="Z18" s="75">
         <f>'건설계획표_26~38'!T41</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="76">
+      <c r="AA18" s="75">
         <f>'건설계획표_26~38'!U41</f>
         <v>0</v>
       </c>
-      <c r="AB18" s="76">
+      <c r="AB18" s="75">
         <f>'건설계획표_26~38'!V41</f>
         <v>0</v>
       </c>
-      <c r="AC18" s="76">
+      <c r="AC18" s="75">
         <f>'건설계획표_26~38'!W41</f>
         <v>0</v>
       </c>
-      <c r="AD18" s="76">
+      <c r="AD18" s="75">
         <f>'건설계획표_26~38'!X41</f>
         <v>0</v>
       </c>
-      <c r="AE18" s="76">
+      <c r="AE18" s="75">
         <f>'건설계획표_26~38'!Y41</f>
         <v>0</v>
       </c>
-      <c r="AF18" s="76">
+      <c r="AF18" s="75">
         <f>'건설계획표_26~38'!Z41</f>
         <v>0</v>
       </c>
-      <c r="AG18" s="76">
+      <c r="AG18" s="75">
         <f>'건설계획표_26~38'!AA41</f>
         <v>0</v>
       </c>
@@ -12174,131 +12482,131 @@
       <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="76">
+      <c r="B19" s="75">
         <f>'설비현황_19~25'!B42</f>
         <v>0</v>
       </c>
-      <c r="C19" s="76">
+      <c r="C19" s="75">
         <f>'설비현황_19~25'!C42</f>
         <v>0</v>
       </c>
-      <c r="D19" s="76">
+      <c r="D19" s="75">
         <f>'설비현황_19~25'!D42</f>
         <v>0</v>
       </c>
-      <c r="E19" s="76">
+      <c r="E19" s="75">
         <f>'설비현황_19~25'!E42</f>
         <v>0</v>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="75">
         <f>'설비현황_19~25'!F42</f>
         <v>0</v>
       </c>
-      <c r="G19" s="76">
+      <c r="G19" s="75">
         <f>'설비현황_19~25'!G42</f>
         <v>0</v>
       </c>
-      <c r="H19" s="76">
+      <c r="H19" s="75">
         <f>'설비현황_19~25'!H42</f>
         <v>0</v>
       </c>
-      <c r="I19" s="76">
+      <c r="I19" s="75">
         <f>'건설계획표_26~38'!C42</f>
         <v>0</v>
       </c>
-      <c r="J19" s="76">
+      <c r="J19" s="75">
         <f>'건설계획표_26~38'!D42</f>
         <v>0</v>
       </c>
-      <c r="K19" s="76">
+      <c r="K19" s="75">
         <f>'건설계획표_26~38'!E42</f>
         <v>0</v>
       </c>
-      <c r="L19" s="76">
+      <c r="L19" s="75">
         <f>'건설계획표_26~38'!F42</f>
         <v>0</v>
       </c>
-      <c r="M19" s="76">
+      <c r="M19" s="75">
         <f>'건설계획표_26~38'!G42</f>
         <v>0</v>
       </c>
-      <c r="N19" s="76">
+      <c r="N19" s="75">
         <f>'건설계획표_26~38'!H42</f>
         <v>0</v>
       </c>
-      <c r="O19" s="76">
+      <c r="O19" s="75">
         <f>'건설계획표_26~38'!I42</f>
         <v>0</v>
       </c>
-      <c r="P19" s="76">
+      <c r="P19" s="75">
         <f>'건설계획표_26~38'!J42</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="76">
+      <c r="Q19" s="75">
         <f>'건설계획표_26~38'!K42</f>
         <v>0</v>
       </c>
-      <c r="R19" s="76">
+      <c r="R19" s="75">
         <f>'건설계획표_26~38'!L42</f>
         <v>0</v>
       </c>
-      <c r="S19" s="76">
+      <c r="S19" s="75">
         <f>'건설계획표_26~38'!M42</f>
         <v>0</v>
       </c>
-      <c r="T19" s="76">
+      <c r="T19" s="75">
         <f>'건설계획표_26~38'!N42</f>
         <v>0</v>
       </c>
-      <c r="U19" s="76">
+      <c r="U19" s="75">
         <f>'건설계획표_26~38'!O42</f>
         <v>1370</v>
       </c>
-      <c r="V19" s="76">
+      <c r="V19" s="75">
         <f>'건설계획표_26~38'!P42</f>
         <v>0</v>
       </c>
-      <c r="W19" s="76">
+      <c r="W19" s="75">
         <f>'건설계획표_26~38'!Q42</f>
         <v>0</v>
       </c>
-      <c r="X19" s="76">
+      <c r="X19" s="75">
         <f>'건설계획표_26~38'!R42</f>
         <v>0</v>
       </c>
-      <c r="Y19" s="76">
+      <c r="Y19" s="75">
         <f>'건설계획표_26~38'!S42</f>
         <v>0</v>
       </c>
-      <c r="Z19" s="76">
+      <c r="Z19" s="75">
         <f>'건설계획표_26~38'!T42</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="76">
+      <c r="AA19" s="75">
         <f>'건설계획표_26~38'!U42</f>
         <v>0</v>
       </c>
-      <c r="AB19" s="76">
+      <c r="AB19" s="75">
         <f>'건설계획표_26~38'!V42</f>
         <v>0</v>
       </c>
-      <c r="AC19" s="76">
+      <c r="AC19" s="75">
         <f>'건설계획표_26~38'!W42</f>
         <v>0</v>
       </c>
-      <c r="AD19" s="76">
+      <c r="AD19" s="75">
         <f>'건설계획표_26~38'!X42</f>
         <v>0</v>
       </c>
-      <c r="AE19" s="76">
+      <c r="AE19" s="75">
         <f>'건설계획표_26~38'!Y42</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="76">
+      <c r="AF19" s="75">
         <f>'건설계획표_26~38'!Z42</f>
         <v>0</v>
       </c>
-      <c r="AG19" s="76">
+      <c r="AG19" s="75">
         <f>'건설계획표_26~38'!AA42</f>
         <v>0</v>
       </c>
@@ -12307,131 +12615,131 @@
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="76">
+      <c r="B20" s="75">
         <f>'설비현황_19~25'!B43</f>
         <v>0</v>
       </c>
-      <c r="C20" s="76">
+      <c r="C20" s="75">
         <f>'설비현황_19~25'!C43</f>
         <v>0</v>
       </c>
-      <c r="D20" s="76">
+      <c r="D20" s="75">
         <f>'설비현황_19~25'!D43</f>
         <v>0</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="75">
         <f>'설비현황_19~25'!E43</f>
         <v>0</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="75">
         <f>'설비현황_19~25'!F43</f>
         <v>0</v>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="75">
         <f>'설비현황_19~25'!G43</f>
         <v>0</v>
       </c>
-      <c r="H20" s="76">
+      <c r="H20" s="75">
         <f>'설비현황_19~25'!H43</f>
         <v>0</v>
       </c>
-      <c r="I20" s="76">
+      <c r="I20" s="75">
         <f>'건설계획표_26~38'!C43</f>
         <v>0</v>
       </c>
-      <c r="J20" s="76">
+      <c r="J20" s="75">
         <f>'건설계획표_26~38'!D43</f>
         <v>0</v>
       </c>
-      <c r="K20" s="76">
+      <c r="K20" s="75">
         <f>'건설계획표_26~38'!E43</f>
         <v>0</v>
       </c>
-      <c r="L20" s="76">
+      <c r="L20" s="75">
         <f>'건설계획표_26~38'!F43</f>
         <v>0</v>
       </c>
-      <c r="M20" s="76">
+      <c r="M20" s="75">
         <f>'건설계획표_26~38'!G43</f>
         <v>0</v>
       </c>
-      <c r="N20" s="76">
+      <c r="N20" s="75">
         <f>'건설계획표_26~38'!H43</f>
         <v>0</v>
       </c>
-      <c r="O20" s="76">
+      <c r="O20" s="75">
         <f>'건설계획표_26~38'!I43</f>
         <v>0</v>
       </c>
-      <c r="P20" s="76">
+      <c r="P20" s="75">
         <f>'건설계획표_26~38'!J43</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="76">
+      <c r="Q20" s="75">
         <f>'건설계획표_26~38'!K43</f>
         <v>0</v>
       </c>
-      <c r="R20" s="76">
+      <c r="R20" s="75">
         <f>'건설계획표_26~38'!L43</f>
         <v>0</v>
       </c>
-      <c r="S20" s="76">
+      <c r="S20" s="75">
         <f>'건설계획표_26~38'!M43</f>
         <v>0</v>
       </c>
-      <c r="T20" s="76">
+      <c r="T20" s="75">
         <f>'건설계획표_26~38'!N43</f>
         <v>0</v>
       </c>
-      <c r="U20" s="76">
+      <c r="U20" s="75">
         <f>'건설계획표_26~38'!O43</f>
         <v>0</v>
       </c>
-      <c r="V20" s="76">
+      <c r="V20" s="75">
         <f>'건설계획표_26~38'!P43</f>
         <v>0</v>
       </c>
-      <c r="W20" s="76">
+      <c r="W20" s="75">
         <f>'건설계획표_26~38'!Q43</f>
         <v>0</v>
       </c>
-      <c r="X20" s="76">
+      <c r="X20" s="75">
         <f>'건설계획표_26~38'!R43</f>
         <v>0</v>
       </c>
-      <c r="Y20" s="76">
+      <c r="Y20" s="75">
         <f>'건설계획표_26~38'!S43</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="76">
+      <c r="Z20" s="75">
         <f>'건설계획표_26~38'!T43</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="76">
+      <c r="AA20" s="75">
         <f>'건설계획표_26~38'!U43</f>
         <v>0</v>
       </c>
-      <c r="AB20" s="76">
+      <c r="AB20" s="75">
         <f>'건설계획표_26~38'!V43</f>
         <v>0</v>
       </c>
-      <c r="AC20" s="76">
+      <c r="AC20" s="75">
         <f>'건설계획표_26~38'!W43</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="76">
+      <c r="AD20" s="75">
         <f>'건설계획표_26~38'!X43</f>
         <v>0</v>
       </c>
-      <c r="AE20" s="76">
+      <c r="AE20" s="75">
         <f>'건설계획표_26~38'!Y43</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="76">
+      <c r="AF20" s="75">
         <f>'건설계획표_26~38'!Z43</f>
         <v>0</v>
       </c>
-      <c r="AG20" s="76">
+      <c r="AG20" s="75">
         <f>'건설계획표_26~38'!AA43</f>
         <v>0</v>
       </c>
@@ -12440,131 +12748,131 @@
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="76">
+      <c r="B21" s="75">
         <f>'설비현황_19~25'!B44</f>
         <v>0</v>
       </c>
-      <c r="C21" s="76">
+      <c r="C21" s="75">
         <f>'설비현황_19~25'!C44</f>
         <v>0</v>
       </c>
-      <c r="D21" s="76">
+      <c r="D21" s="75">
         <f>'설비현황_19~25'!D44</f>
         <v>0</v>
       </c>
-      <c r="E21" s="76">
+      <c r="E21" s="75">
         <f>'설비현황_19~25'!E44</f>
         <v>0</v>
       </c>
-      <c r="F21" s="76">
+      <c r="F21" s="75">
         <f>'설비현황_19~25'!F44</f>
         <v>0</v>
       </c>
-      <c r="G21" s="76">
+      <c r="G21" s="75">
         <f>'설비현황_19~25'!G44</f>
         <v>0</v>
       </c>
-      <c r="H21" s="76">
+      <c r="H21" s="75">
         <f>'설비현황_19~25'!H44</f>
         <v>0</v>
       </c>
-      <c r="I21" s="76">
+      <c r="I21" s="75">
         <f>'건설계획표_26~38'!C44</f>
         <v>0</v>
       </c>
-      <c r="J21" s="76">
+      <c r="J21" s="75">
         <f>'건설계획표_26~38'!D44</f>
         <v>0</v>
       </c>
-      <c r="K21" s="76">
+      <c r="K21" s="75">
         <f>'건설계획표_26~38'!E44</f>
         <v>0</v>
       </c>
-      <c r="L21" s="76">
+      <c r="L21" s="75">
         <f>'건설계획표_26~38'!F44</f>
         <v>0</v>
       </c>
-      <c r="M21" s="76">
+      <c r="M21" s="75">
         <f>'건설계획표_26~38'!G44</f>
         <v>0</v>
       </c>
-      <c r="N21" s="76">
+      <c r="N21" s="75">
         <f>'건설계획표_26~38'!H44</f>
         <v>0</v>
       </c>
-      <c r="O21" s="76">
+      <c r="O21" s="75">
         <f>'건설계획표_26~38'!I44</f>
         <v>0</v>
       </c>
-      <c r="P21" s="76">
+      <c r="P21" s="75">
         <f>'건설계획표_26~38'!J44</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="76">
+      <c r="Q21" s="75">
         <f>'건설계획표_26~38'!K44</f>
         <v>0</v>
       </c>
-      <c r="R21" s="76">
+      <c r="R21" s="75">
         <f>'건설계획표_26~38'!L44</f>
         <v>0</v>
       </c>
-      <c r="S21" s="76">
+      <c r="S21" s="75">
         <f>'건설계획표_26~38'!M44</f>
         <v>0</v>
       </c>
-      <c r="T21" s="76">
+      <c r="T21" s="75">
         <f>'건설계획표_26~38'!N44</f>
         <v>0</v>
       </c>
-      <c r="U21" s="76">
+      <c r="U21" s="75">
         <f>'건설계획표_26~38'!O44</f>
         <v>0</v>
       </c>
-      <c r="V21" s="76">
+      <c r="V21" s="75">
         <f>'건설계획표_26~38'!P44</f>
         <v>0</v>
       </c>
-      <c r="W21" s="76">
+      <c r="W21" s="75">
         <f>'건설계획표_26~38'!Q44</f>
         <v>0</v>
       </c>
-      <c r="X21" s="76">
+      <c r="X21" s="75">
         <f>'건설계획표_26~38'!R44</f>
         <v>0</v>
       </c>
-      <c r="Y21" s="76">
+      <c r="Y21" s="75">
         <f>'건설계획표_26~38'!S44</f>
         <v>0</v>
       </c>
-      <c r="Z21" s="76">
+      <c r="Z21" s="75">
         <f>'건설계획표_26~38'!T44</f>
         <v>0</v>
       </c>
-      <c r="AA21" s="76">
+      <c r="AA21" s="75">
         <f>'건설계획표_26~38'!U44</f>
         <v>0</v>
       </c>
-      <c r="AB21" s="76">
+      <c r="AB21" s="75">
         <f>'건설계획표_26~38'!V44</f>
         <v>0</v>
       </c>
-      <c r="AC21" s="76">
+      <c r="AC21" s="75">
         <f>'건설계획표_26~38'!W44</f>
         <v>0</v>
       </c>
-      <c r="AD21" s="76">
+      <c r="AD21" s="75">
         <f>'건설계획표_26~38'!X44</f>
         <v>0</v>
       </c>
-      <c r="AE21" s="76">
+      <c r="AE21" s="75">
         <f>'건설계획표_26~38'!Y44</f>
         <v>0</v>
       </c>
-      <c r="AF21" s="76">
+      <c r="AF21" s="75">
         <f>'건설계획표_26~38'!Z44</f>
         <v>0</v>
       </c>
-      <c r="AG21" s="76">
+      <c r="AG21" s="75">
         <f>'건설계획표_26~38'!AA44</f>
         <v>0</v>
       </c>
@@ -12573,131 +12881,131 @@
       <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="76">
+      <c r="B22" s="75">
         <f>'설비현황_19~25'!B45</f>
         <v>0</v>
       </c>
-      <c r="C22" s="76">
+      <c r="C22" s="75">
         <f>'설비현황_19~25'!C45</f>
         <v>0</v>
       </c>
-      <c r="D22" s="76">
+      <c r="D22" s="75">
         <f>'설비현황_19~25'!D45</f>
         <v>0</v>
       </c>
-      <c r="E22" s="76">
+      <c r="E22" s="75">
         <f>'설비현황_19~25'!E45</f>
         <v>0</v>
       </c>
-      <c r="F22" s="76">
+      <c r="F22" s="75">
         <f>'설비현황_19~25'!F45</f>
         <v>0</v>
       </c>
-      <c r="G22" s="76">
+      <c r="G22" s="75">
         <f>'설비현황_19~25'!G45</f>
         <v>0</v>
       </c>
-      <c r="H22" s="76">
+      <c r="H22" s="75">
         <f>'설비현황_19~25'!H45</f>
         <v>0</v>
       </c>
-      <c r="I22" s="76">
+      <c r="I22" s="75">
         <f>'건설계획표_26~38'!C45</f>
         <v>0</v>
       </c>
-      <c r="J22" s="76">
+      <c r="J22" s="75">
         <f>'건설계획표_26~38'!D45</f>
         <v>0</v>
       </c>
-      <c r="K22" s="76">
+      <c r="K22" s="75">
         <f>'건설계획표_26~38'!E45</f>
         <v>0</v>
       </c>
-      <c r="L22" s="76">
+      <c r="L22" s="75">
         <f>'건설계획표_26~38'!F45</f>
         <v>0</v>
       </c>
-      <c r="M22" s="76">
+      <c r="M22" s="75">
         <f>'건설계획표_26~38'!G45</f>
         <v>0</v>
       </c>
-      <c r="N22" s="76">
+      <c r="N22" s="75">
         <f>'건설계획표_26~38'!H45</f>
         <v>0</v>
       </c>
-      <c r="O22" s="76">
+      <c r="O22" s="75">
         <f>'건설계획표_26~38'!I45</f>
         <v>0</v>
       </c>
-      <c r="P22" s="76">
+      <c r="P22" s="75">
         <f>'건설계획표_26~38'!J45</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="76">
+      <c r="Q22" s="75">
         <f>'건설계획표_26~38'!K45</f>
         <v>0</v>
       </c>
-      <c r="R22" s="76">
+      <c r="R22" s="75">
         <f>'건설계획표_26~38'!L45</f>
         <v>0</v>
       </c>
-      <c r="S22" s="76">
+      <c r="S22" s="75">
         <f>'건설계획표_26~38'!M45</f>
         <v>0</v>
       </c>
-      <c r="T22" s="76">
+      <c r="T22" s="75">
         <f>'건설계획표_26~38'!N45</f>
         <v>0</v>
       </c>
-      <c r="U22" s="76">
+      <c r="U22" s="75">
         <f>'건설계획표_26~38'!O45</f>
         <v>0</v>
       </c>
-      <c r="V22" s="76">
+      <c r="V22" s="75">
         <f>'건설계획표_26~38'!P45</f>
         <v>0</v>
       </c>
-      <c r="W22" s="76">
+      <c r="W22" s="75">
         <f>'건설계획표_26~38'!Q45</f>
         <v>0</v>
       </c>
-      <c r="X22" s="76">
+      <c r="X22" s="75">
         <f>'건설계획표_26~38'!R45</f>
         <v>0</v>
       </c>
-      <c r="Y22" s="76">
+      <c r="Y22" s="75">
         <f>'건설계획표_26~38'!S45</f>
         <v>0</v>
       </c>
-      <c r="Z22" s="76">
+      <c r="Z22" s="75">
         <f>'건설계획표_26~38'!T45</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="76">
+      <c r="AA22" s="75">
         <f>'건설계획표_26~38'!U45</f>
         <v>0</v>
       </c>
-      <c r="AB22" s="76">
+      <c r="AB22" s="75">
         <f>'건설계획표_26~38'!V45</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="76">
+      <c r="AC22" s="75">
         <f>'건설계획표_26~38'!W45</f>
         <v>0</v>
       </c>
-      <c r="AD22" s="76">
+      <c r="AD22" s="75">
         <f>'건설계획표_26~38'!X45</f>
         <v>0</v>
       </c>
-      <c r="AE22" s="76">
+      <c r="AE22" s="75">
         <f>'건설계획표_26~38'!Y45</f>
         <v>0</v>
       </c>
-      <c r="AF22" s="76">
+      <c r="AF22" s="75">
         <f>'건설계획표_26~38'!Z45</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="76">
+      <c r="AG22" s="75">
         <f>'건설계획표_26~38'!AA45</f>
         <v>0</v>
       </c>
@@ -12706,131 +13014,131 @@
       <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="76">
+      <c r="B23" s="75">
         <f>'설비현황_19~25'!B46</f>
         <v>0</v>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="75">
         <f>'설비현황_19~25'!C46</f>
         <v>0</v>
       </c>
-      <c r="D23" s="76">
+      <c r="D23" s="75">
         <f>'설비현황_19~25'!D46</f>
         <v>0</v>
       </c>
-      <c r="E23" s="76">
+      <c r="E23" s="75">
         <f>'설비현황_19~25'!E46</f>
         <v>0</v>
       </c>
-      <c r="F23" s="76">
+      <c r="F23" s="75">
         <f>'설비현황_19~25'!F46</f>
         <v>0</v>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="75">
         <f>'설비현황_19~25'!G46</f>
         <v>0</v>
       </c>
-      <c r="H23" s="76">
+      <c r="H23" s="75">
         <f>'설비현황_19~25'!H46</f>
         <v>0</v>
       </c>
-      <c r="I23" s="76">
+      <c r="I23" s="75">
         <f>'건설계획표_26~38'!C46</f>
         <v>0</v>
       </c>
-      <c r="J23" s="76">
+      <c r="J23" s="75">
         <f>'건설계획표_26~38'!D46</f>
         <v>0</v>
       </c>
-      <c r="K23" s="76">
+      <c r="K23" s="75">
         <f>'건설계획표_26~38'!E46</f>
         <v>0</v>
       </c>
-      <c r="L23" s="76">
+      <c r="L23" s="75">
         <f>'건설계획표_26~38'!F46</f>
         <v>0</v>
       </c>
-      <c r="M23" s="76">
+      <c r="M23" s="75">
         <f>'건설계획표_26~38'!G46</f>
         <v>0</v>
       </c>
-      <c r="N23" s="76">
+      <c r="N23" s="75">
         <f>'건설계획표_26~38'!H46</f>
         <v>0</v>
       </c>
-      <c r="O23" s="76">
+      <c r="O23" s="75">
         <f>'건설계획표_26~38'!I46</f>
         <v>0</v>
       </c>
-      <c r="P23" s="76">
+      <c r="P23" s="75">
         <f>'건설계획표_26~38'!J46</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="76">
+      <c r="Q23" s="75">
         <f>'건설계획표_26~38'!K46</f>
         <v>350</v>
       </c>
-      <c r="R23" s="76">
+      <c r="R23" s="75">
         <f>'건설계획표_26~38'!L46</f>
         <v>350</v>
       </c>
-      <c r="S23" s="76">
+      <c r="S23" s="75">
         <f>'건설계획표_26~38'!M46</f>
         <v>0</v>
       </c>
-      <c r="T23" s="76">
+      <c r="T23" s="75">
         <f>'건설계획표_26~38'!N46</f>
         <v>0</v>
       </c>
-      <c r="U23" s="76">
+      <c r="U23" s="75">
         <f>'건설계획표_26~38'!O46</f>
         <v>0</v>
       </c>
-      <c r="V23" s="76">
+      <c r="V23" s="75">
         <f>'건설계획표_26~38'!P46</f>
         <v>0</v>
       </c>
-      <c r="W23" s="76">
+      <c r="W23" s="75">
         <f>'건설계획표_26~38'!Q46</f>
         <v>0</v>
       </c>
-      <c r="X23" s="76">
+      <c r="X23" s="75">
         <f>'건설계획표_26~38'!R46</f>
         <v>0</v>
       </c>
-      <c r="Y23" s="76">
+      <c r="Y23" s="75">
         <f>'건설계획표_26~38'!S46</f>
         <v>0</v>
       </c>
-      <c r="Z23" s="76">
+      <c r="Z23" s="75">
         <f>'건설계획표_26~38'!T46</f>
         <v>0</v>
       </c>
-      <c r="AA23" s="76">
+      <c r="AA23" s="75">
         <f>'건설계획표_26~38'!U46</f>
         <v>0</v>
       </c>
-      <c r="AB23" s="76">
+      <c r="AB23" s="75">
         <f>'건설계획표_26~38'!V46</f>
         <v>0</v>
       </c>
-      <c r="AC23" s="76">
+      <c r="AC23" s="75">
         <f>'건설계획표_26~38'!W46</f>
         <v>0</v>
       </c>
-      <c r="AD23" s="76">
+      <c r="AD23" s="75">
         <f>'건설계획표_26~38'!X46</f>
         <v>0</v>
       </c>
-      <c r="AE23" s="76">
+      <c r="AE23" s="75">
         <f>'건설계획표_26~38'!Y46</f>
         <v>0</v>
       </c>
-      <c r="AF23" s="76">
+      <c r="AF23" s="75">
         <f>'건설계획표_26~38'!Z46</f>
         <v>0</v>
       </c>
-      <c r="AG23" s="76">
+      <c r="AG23" s="75">
         <f>'건설계획표_26~38'!AA46</f>
         <v>0</v>
       </c>
@@ -12839,131 +13147,131 @@
       <c r="A24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="76">
+      <c r="B24" s="75">
         <f>'설비현황_19~25'!B47</f>
         <v>0</v>
       </c>
-      <c r="C24" s="76">
+      <c r="C24" s="75">
         <f>'설비현황_19~25'!C47</f>
         <v>0</v>
       </c>
-      <c r="D24" s="76">
+      <c r="D24" s="75">
         <f>'설비현황_19~25'!D47</f>
         <v>0</v>
       </c>
-      <c r="E24" s="76">
+      <c r="E24" s="75">
         <f>'설비현황_19~25'!E47</f>
         <v>0</v>
       </c>
-      <c r="F24" s="76">
+      <c r="F24" s="75">
         <f>'설비현황_19~25'!F47</f>
         <v>0</v>
       </c>
-      <c r="G24" s="76">
+      <c r="G24" s="75">
         <f>'설비현황_19~25'!G47</f>
         <v>0</v>
       </c>
-      <c r="H24" s="76">
+      <c r="H24" s="75">
         <f>'설비현황_19~25'!H47</f>
         <v>0</v>
       </c>
-      <c r="I24" s="76">
+      <c r="I24" s="75">
         <f>'건설계획표_26~38'!C47</f>
         <v>0</v>
       </c>
-      <c r="J24" s="76">
+      <c r="J24" s="75">
         <f>'건설계획표_26~38'!D47</f>
         <v>0</v>
       </c>
-      <c r="K24" s="76">
+      <c r="K24" s="75">
         <f>'건설계획표_26~38'!E47</f>
         <v>0</v>
       </c>
-      <c r="L24" s="76">
+      <c r="L24" s="75">
         <f>'건설계획표_26~38'!F47</f>
         <v>0</v>
       </c>
-      <c r="M24" s="76">
+      <c r="M24" s="75">
         <f>'건설계획표_26~38'!G47</f>
         <v>0</v>
       </c>
-      <c r="N24" s="76">
+      <c r="N24" s="75">
         <f>'건설계획표_26~38'!H47</f>
         <v>0</v>
       </c>
-      <c r="O24" s="76">
+      <c r="O24" s="75">
         <f>'건설계획표_26~38'!I47</f>
         <v>0</v>
       </c>
-      <c r="P24" s="76">
+      <c r="P24" s="75">
         <f>'건설계획표_26~38'!J47</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="76">
+      <c r="Q24" s="75">
         <f>'건설계획표_26~38'!K47</f>
         <v>0</v>
       </c>
-      <c r="R24" s="76">
+      <c r="R24" s="75">
         <f>'건설계획표_26~38'!L47</f>
         <v>0</v>
       </c>
-      <c r="S24" s="76">
+      <c r="S24" s="75">
         <f>'건설계획표_26~38'!M47</f>
         <v>0</v>
       </c>
-      <c r="T24" s="76">
+      <c r="T24" s="75">
         <f>'건설계획표_26~38'!N47</f>
         <v>0</v>
       </c>
-      <c r="U24" s="76">
+      <c r="U24" s="75">
         <f>'건설계획표_26~38'!O47</f>
         <v>0</v>
       </c>
-      <c r="V24" s="76">
+      <c r="V24" s="75">
         <f>'건설계획표_26~38'!P47</f>
         <v>0</v>
       </c>
-      <c r="W24" s="76">
+      <c r="W24" s="75">
         <f>'건설계획표_26~38'!Q47</f>
         <v>0</v>
       </c>
-      <c r="X24" s="76">
+      <c r="X24" s="75">
         <f>'건설계획표_26~38'!R47</f>
         <v>0</v>
       </c>
-      <c r="Y24" s="76">
+      <c r="Y24" s="75">
         <f>'건설계획표_26~38'!S47</f>
         <v>0</v>
       </c>
-      <c r="Z24" s="76">
+      <c r="Z24" s="75">
         <f>'건설계획표_26~38'!T47</f>
         <v>0</v>
       </c>
-      <c r="AA24" s="76">
+      <c r="AA24" s="75">
         <f>'건설계획표_26~38'!U47</f>
         <v>0</v>
       </c>
-      <c r="AB24" s="76">
+      <c r="AB24" s="75">
         <f>'건설계획표_26~38'!V47</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="76">
+      <c r="AC24" s="75">
         <f>'건설계획표_26~38'!W47</f>
         <v>0</v>
       </c>
-      <c r="AD24" s="76">
+      <c r="AD24" s="75">
         <f>'건설계획표_26~38'!X47</f>
         <v>0</v>
       </c>
-      <c r="AE24" s="76">
+      <c r="AE24" s="75">
         <f>'건설계획표_26~38'!Y47</f>
         <v>0</v>
       </c>
-      <c r="AF24" s="76">
+      <c r="AF24" s="75">
         <f>'건설계획표_26~38'!Z47</f>
         <v>0</v>
       </c>
-      <c r="AG24" s="76">
+      <c r="AG24" s="75">
         <f>'건설계획표_26~38'!AA47</f>
         <v>0</v>
       </c>
@@ -12972,131 +13280,131 @@
       <c r="A25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="76">
+      <c r="B25" s="75">
         <f>'설비현황_19~25'!B48</f>
         <v>0</v>
       </c>
-      <c r="C25" s="76">
+      <c r="C25" s="75">
         <f>'설비현황_19~25'!C48</f>
         <v>0</v>
       </c>
-      <c r="D25" s="76">
+      <c r="D25" s="75">
         <f>'설비현황_19~25'!D48</f>
         <v>0</v>
       </c>
-      <c r="E25" s="76">
+      <c r="E25" s="75">
         <f>'설비현황_19~25'!E48</f>
         <v>0</v>
       </c>
-      <c r="F25" s="76">
+      <c r="F25" s="75">
         <f>'설비현황_19~25'!F48</f>
         <v>0</v>
       </c>
-      <c r="G25" s="76">
+      <c r="G25" s="75">
         <f>'설비현황_19~25'!G48</f>
         <v>0</v>
       </c>
-      <c r="H25" s="76">
+      <c r="H25" s="75">
         <f>'설비현황_19~25'!H48</f>
         <v>0</v>
       </c>
-      <c r="I25" s="76">
+      <c r="I25" s="75">
         <f>'건설계획표_26~38'!C48</f>
         <v>0</v>
       </c>
-      <c r="J25" s="76">
+      <c r="J25" s="75">
         <f>'건설계획표_26~38'!D48</f>
         <v>0</v>
       </c>
-      <c r="K25" s="76">
+      <c r="K25" s="75">
         <f>'건설계획표_26~38'!E48</f>
         <v>0</v>
       </c>
-      <c r="L25" s="76">
+      <c r="L25" s="75">
         <f>'건설계획표_26~38'!F48</f>
         <v>0</v>
       </c>
-      <c r="M25" s="76">
+      <c r="M25" s="75">
         <f>'건설계획표_26~38'!G48</f>
         <v>0</v>
       </c>
-      <c r="N25" s="76">
+      <c r="N25" s="75">
         <f>'건설계획표_26~38'!H48</f>
         <v>0</v>
       </c>
-      <c r="O25" s="76">
+      <c r="O25" s="75">
         <f>'건설계획표_26~38'!I48</f>
         <v>0</v>
       </c>
-      <c r="P25" s="76">
+      <c r="P25" s="75">
         <f>'건설계획표_26~38'!J48</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="76">
+      <c r="Q25" s="75">
         <f>'건설계획표_26~38'!K48</f>
         <v>0</v>
       </c>
-      <c r="R25" s="76">
+      <c r="R25" s="75">
         <f>'건설계획표_26~38'!L48</f>
         <v>0</v>
       </c>
-      <c r="S25" s="76">
+      <c r="S25" s="75">
         <f>'건설계획표_26~38'!M48</f>
         <v>0</v>
       </c>
-      <c r="T25" s="76">
+      <c r="T25" s="75">
         <f>'건설계획표_26~38'!N48</f>
         <v>1870</v>
       </c>
-      <c r="U25" s="76">
+      <c r="U25" s="75">
         <f>'건설계획표_26~38'!O48</f>
         <v>1550</v>
       </c>
-      <c r="V25" s="76">
+      <c r="V25" s="75">
         <f>'건설계획표_26~38'!P48</f>
         <v>0</v>
       </c>
-      <c r="W25" s="76">
+      <c r="W25" s="75">
         <f>'건설계획표_26~38'!Q48</f>
         <v>0</v>
       </c>
-      <c r="X25" s="76">
+      <c r="X25" s="75">
         <f>'건설계획표_26~38'!R48</f>
         <v>0</v>
       </c>
-      <c r="Y25" s="76">
+      <c r="Y25" s="75">
         <f>'건설계획표_26~38'!S48</f>
         <v>0</v>
       </c>
-      <c r="Z25" s="76">
+      <c r="Z25" s="75">
         <f>'건설계획표_26~38'!T48</f>
         <v>0</v>
       </c>
-      <c r="AA25" s="76">
+      <c r="AA25" s="75">
         <f>'건설계획표_26~38'!U48</f>
         <v>0</v>
       </c>
-      <c r="AB25" s="76">
+      <c r="AB25" s="75">
         <f>'건설계획표_26~38'!V48</f>
         <v>0</v>
       </c>
-      <c r="AC25" s="76">
+      <c r="AC25" s="75">
         <f>'건설계획표_26~38'!W48</f>
         <v>0</v>
       </c>
-      <c r="AD25" s="76">
+      <c r="AD25" s="75">
         <f>'건설계획표_26~38'!X48</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="76">
+      <c r="AE25" s="75">
         <f>'건설계획표_26~38'!Y48</f>
         <v>0</v>
       </c>
-      <c r="AF25" s="76">
+      <c r="AF25" s="75">
         <f>'건설계획표_26~38'!Z48</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="76">
+      <c r="AG25" s="75">
         <f>'건설계획표_26~38'!AA48</f>
         <v>0</v>
       </c>
@@ -13110,16 +13418,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="688c5d3b-a76a-458b-b159-91c2a1154680">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010027350D42B0D95040ACC873ED5DCB146E" ma:contentTypeVersion="10" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="c2e4f52adf7af47ba555973ff8cbcabe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="688c5d3b-a76a-458b-b159-91c2a1154680" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="502e33886199ad3dabc1cc93359c84e5" ns2:_="">
     <xsd:import namespace="688c5d3b-a76a-458b-b159-91c2a1154680"/>
@@ -13295,7 +13593,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -13304,17 +13602,17 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13444BB4-D2AE-4704-9F59-09418FDD2FE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="688c5d3b-a76a-458b-b159-91c2a1154680"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="688c5d3b-a76a-458b-b159-91c2a1154680">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C8EFB68-B099-4082-B802-B144AFACC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13332,10 +13630,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AC0E8B6-FC6C-47AD-8E91-EBF41CCB1712}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13444BB4-D2AE-4704-9F59-09418FDD2FE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="688c5d3b-a76a-458b-b159-91c2a1154680"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
